--- a/Transfer_vehicle_DB 25 redux.xlsx
+++ b/Transfer_vehicle_DB 25 redux.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\ORLA_Lander_Mission_Architecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA7FC8B5-0A27-4D4E-A390-DCBBE517981D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68507EBB-3A98-4A78-8FA6-F35BEEA28680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30450" yWindow="435" windowWidth="21600" windowHeight="13845" tabRatio="770" xr2:uid="{EAA8122F-796E-42AA-B602-9BE6D85E3BA4}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="770" xr2:uid="{EAA8122F-796E-42AA-B602-9BE6D85E3BA4}"/>
   </bookViews>
   <sheets>
     <sheet name="TV database" sheetId="2" r:id="rId1"/>
@@ -820,7 +820,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1012,19 +1012,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -28481,7 +28480,7 @@
         <v>5361</v>
       </c>
       <c r="G2" s="24">
-        <f>0.5*(C2)*F2^2</f>
+        <f t="shared" ref="G2:G11" si="0">0.5*(C2)*F2^2</f>
         <v>280218129750</v>
       </c>
       <c r="H2" s="16" t="s">
@@ -28515,7 +28514,7 @@
         <v>6015.0948447352202</v>
       </c>
       <c r="G3" s="24">
-        <f>0.5*(C3)*F3^2</f>
+        <f t="shared" si="0"/>
         <v>130795638058.0442</v>
       </c>
       <c r="H3" s="16" t="s">
@@ -28555,7 +28554,7 @@
         <v>3076</v>
       </c>
       <c r="G4" s="24">
-        <f>0.5*(C4)*F4^2</f>
+        <f t="shared" si="0"/>
         <v>100824685056</v>
       </c>
       <c r="H4" s="70" t="s">
@@ -28591,7 +28590,7 @@
         <v>13064.039525375183</v>
       </c>
       <c r="G5" s="24">
-        <f>0.5*(C5)*F5^2</f>
+        <f t="shared" si="0"/>
         <v>67584974973.343758</v>
       </c>
       <c r="H5" s="16" t="s">
@@ -28631,7 +28630,7 @@
         <v>1910</v>
       </c>
       <c r="G6" s="24">
-        <f>0.5*(C6)*F6^2</f>
+        <f t="shared" si="0"/>
         <v>48277131350</v>
       </c>
       <c r="H6" s="16" t="s">
@@ -28665,7 +28664,7 @@
         <v>2350</v>
       </c>
       <c r="G7" s="24">
-        <f>0.5*(C7)*F7^2</f>
+        <f t="shared" si="0"/>
         <v>42537056250</v>
       </c>
       <c r="H7" s="16" t="s">
@@ -28699,7 +28698,7 @@
         <v>8134.531274289594</v>
       </c>
       <c r="G8" s="24">
-        <f>0.5*(C8)*F8^2</f>
+        <f t="shared" si="0"/>
         <v>16542649763.098871</v>
       </c>
       <c r="H8" s="16" t="s">
@@ -28739,7 +28738,7 @@
         <v>8047.6691416498415</v>
       </c>
       <c r="G9" s="24">
-        <f>0.5*(C9)*F9^2</f>
+        <f t="shared" si="0"/>
         <v>12078668511.410868</v>
       </c>
       <c r="H9" s="16" t="s">
@@ -28780,7 +28779,7 @@
         <v>2051.957210326525</v>
       </c>
       <c r="G10" s="24">
-        <f>0.5*(C10)*F10^2</f>
+        <f t="shared" si="0"/>
         <v>9263162464.6242332</v>
       </c>
       <c r="H10" s="16" t="s">
@@ -28789,7 +28788,7 @@
       <c r="I10" s="16">
         <v>336</v>
       </c>
-      <c r="L10" s="81" t="s">
+      <c r="L10" t="s">
         <v>121</v>
       </c>
     </row>
@@ -28817,7 +28816,7 @@
         <v>1938.5709356467189</v>
       </c>
       <c r="G11" s="24">
-        <f>0.5*(C11)*F11^2</f>
+        <f t="shared" si="0"/>
         <v>4045548653.8830614</v>
       </c>
       <c r="H11" s="16" t="s">
@@ -28828,7 +28827,7 @@
       </c>
       <c r="J11" s="16"/>
       <c r="K11" s="16"/>
-      <c r="L11" s="81" t="s">
+      <c r="L11" t="s">
         <v>116</v>
       </c>
     </row>
@@ -68580,22 +68579,22 @@
     </row>
     <row r="4" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="77" t="s">
+      <c r="C5" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="78"/>
-      <c r="F5" s="77" t="s">
+      <c r="D5" s="80"/>
+      <c r="F5" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="78"/>
-      <c r="I5" s="77" t="s">
+      <c r="G5" s="80"/>
+      <c r="I5" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="78"/>
-      <c r="L5" s="77" t="s">
+      <c r="J5" s="80"/>
+      <c r="L5" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="78"/>
+      <c r="M5" s="80"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
@@ -68668,11 +68667,11 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="79">
+      <c r="C9" s="77">
         <f>SQRT(D8*((2/D7)-(1/D6)))</f>
         <v>1.9186316480773129</v>
       </c>
-      <c r="D9" s="80"/>
+      <c r="D9" s="78"/>
       <c r="F9" s="6" t="s">
         <v>0</v>
       </c>
@@ -68690,11 +68689,11 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F10" s="79">
+      <c r="F10" s="77">
         <f>($G$6-$G$7*EXP((G8)/($G$9*9.81)))/(EXP((G8)/($G$9*9.81)))</f>
         <v>69988.034237650369</v>
       </c>
-      <c r="G10" s="80"/>
+      <c r="G10" s="78"/>
       <c r="I10" s="1" t="s">
         <v>19</v>
       </c>
@@ -68712,10 +68711,10 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C12" s="77" t="s">
+      <c r="C12" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="78"/>
+      <c r="D12" s="80"/>
       <c r="I12" s="6" t="s">
         <v>18</v>
       </c>
@@ -68731,15 +68730,15 @@
       <c r="D13" s="5">
         <v>3558</v>
       </c>
-      <c r="F13" s="77" t="s">
+      <c r="F13" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="78"/>
-      <c r="I13" s="77">
+      <c r="G13" s="80"/>
+      <c r="I13" s="79">
         <f>J12+J11</f>
         <v>5.6429999999999998</v>
       </c>
-      <c r="J13" s="78"/>
+      <c r="J13" s="80"/>
     </row>
     <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C14" s="6" t="s">
@@ -68756,11 +68755,11 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C15" s="77">
+      <c r="C15" s="79">
         <f>(D13+D14)/2</f>
         <v>3558</v>
       </c>
-      <c r="D15" s="78"/>
+      <c r="D15" s="80"/>
       <c r="F15" s="1" t="s">
         <v>6</v>
       </c>
@@ -68775,10 +68774,10 @@
       <c r="G16" s="2">
         <v>1280</v>
       </c>
-      <c r="I16" s="77" t="s">
+      <c r="I16" s="79" t="s">
         <v>95</v>
       </c>
-      <c r="J16" s="78"/>
+      <c r="J16" s="80"/>
     </row>
     <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F17" s="6" t="s">
@@ -68795,15 +68794,15 @@
       </c>
     </row>
     <row r="18" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C18" s="77" t="s">
+      <c r="C18" s="79" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="78"/>
-      <c r="F18" s="79">
+      <c r="D18" s="80"/>
+      <c r="F18" s="77">
         <f>EXP(G16/(G17*9.81))*(G14+G15) - (G14+G15)</f>
         <v>17465.040076315519</v>
       </c>
-      <c r="G18" s="80"/>
+      <c r="G18" s="78"/>
       <c r="I18" s="1" t="s">
         <v>97</v>
       </c>
@@ -68842,16 +68841,16 @@
       </c>
     </row>
     <row r="21" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="79">
+      <c r="C21" s="77">
         <f>2*PI()*SQRT(D19^3/D20)/60/60/24</f>
         <v>2.44459204577962E-2</v>
       </c>
-      <c r="D21" s="80"/>
-      <c r="I21" s="79">
+      <c r="D21" s="78"/>
+      <c r="I21" s="77">
         <f>(J17-J18)/((J19)/(J20))+J18</f>
         <v>1849.3733062330625</v>
       </c>
-      <c r="J21" s="80"/>
+      <c r="J21" s="78"/>
     </row>
     <row r="23" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
@@ -68865,13 +68864,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C18:D18"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="C5:D5"/>
@@ -68880,6 +68872,13 @@
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="C12:D12"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Transfer_vehicle_DB 25 redux.xlsx
+++ b/Transfer_vehicle_DB 25 redux.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\ORLA_Lander_Mission_Architecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68507EBB-3A98-4A78-8FA6-F35BEEA28680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9F0B68-2291-4356-9E25-F5D60DDBF2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="770" xr2:uid="{EAA8122F-796E-42AA-B602-9BE6D85E3BA4}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="770" xr2:uid="{EAA8122F-796E-42AA-B602-9BE6D85E3BA4}"/>
   </bookViews>
   <sheets>
     <sheet name="TV database" sheetId="2" r:id="rId1"/>
@@ -394,10 +394,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>https://web.archive.org/web/20190714030717/https://timesofindia.indiatimes.com/india/chandrayaan-2-all-you-need-to-know-about-indias-2nd-moon-mission/articleshow/70207662.cms
-http://www.astronautix.com/m/monmmh.html</t>
-  </si>
-  <si>
     <t>MON4/MMH</t>
   </si>
   <si>
@@ -411,6 +407,11 @@
   </si>
   <si>
     <t>https://mp.weixin.qq.com/s/xOo0111QseI6CoOurNwbDQ</t>
+  </si>
+  <si>
+    <t>https://web.archive.org/web/20190714030717/https://timesofindia.indiatimes.com/india/chandrayaan-2-all-you-need-to-know-about-indias-2nd-moon-mission/articleshow/70207662.cms
+https://www.isro.gov.in/media_isro/pdf/GSLVMkIII_M1.pdf
+http://www.astronautix.com/m/monmmh.html</t>
   </si>
 </sst>
 </file>
@@ -820,7 +821,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1012,18 +1013,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -28406,22 +28408,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71D78165-C53E-43F9-8039-A8FABD38D39A}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.88671875" customWidth="1"/>
-    <col min="2" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-    <col min="5" max="5" width="27.109375" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" customWidth="1"/>
+    <col min="2" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="5" max="5" width="27.140625" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
     <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.109375" customWidth="1"/>
-    <col min="11" max="11" width="15.33203125" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" customWidth="1"/>
+    <col min="11" max="11" width="15.28515625" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="66" t="s">
         <v>115</v>
       </c>
@@ -28459,7 +28461,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>30</v>
       </c>
@@ -28493,7 +28495,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>75</v>
       </c>
@@ -28533,7 +28535,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="70" t="s">
         <v>106</v>
       </c>
@@ -28569,7 +28571,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>90</v>
       </c>
@@ -28609,7 +28611,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>57</v>
       </c>
@@ -28643,7 +28645,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>51</v>
       </c>
@@ -28677,7 +28679,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>83</v>
       </c>
@@ -28717,7 +28719,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>84</v>
       </c>
@@ -28757,9 +28759,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B10" s="16">
         <v>600</v>
@@ -28783,18 +28785,18 @@
         <v>9263162464.6242332</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I10" s="16">
         <v>336</v>
       </c>
       <c r="L10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B11" s="16">
         <f>682-90</f>
@@ -28820,21 +28822,23 @@
         <v>4045548653.8830614</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I11" s="16">
         <v>340</v>
       </c>
       <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K11" s="16">
+        <v>1000</v>
+      </c>
+      <c r="L11" s="81" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H13" s="16"/>
     </row>
   </sheetData>
@@ -28853,20 +28857,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{304DD466-033E-47B5-BE91-F9755818BF21}">
   <dimension ref="A1:U527"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.42578125" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.33203125" customWidth="1"/>
-    <col min="11" max="11" width="10.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" customWidth="1"/>
     <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="13.88671875" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>32</v>
       </c>
@@ -28923,7 +28927,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>450</v>
       </c>
@@ -28986,7 +28990,7 @@
         <v>2929.8526289031806</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B3" s="14">
         <v>2100</v>
       </c>
@@ -29046,7 +29050,7 @@
         <v>5283.7372678310185</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="19"/>
       <c r="B4" s="20">
         <v>2200</v>
@@ -29107,7 +29111,7 @@
         <v>7637.6219067588609</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="19"/>
       <c r="B5" s="20">
         <v>2300</v>
@@ -29168,7 +29172,7 @@
         <v>9991.5065456866978</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="19"/>
       <c r="B6" s="14">
         <v>2400</v>
@@ -29229,7 +29233,7 @@
         <v>12345.391184614538</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="19"/>
       <c r="B7" s="20">
         <v>2500</v>
@@ -29290,7 +29294,7 @@
         <v>14699.275823542375</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="19"/>
       <c r="B8" s="20">
         <v>2600</v>
@@ -29351,7 +29355,7 @@
         <v>17053.160462470216</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="19"/>
       <c r="B9" s="14">
         <v>2700</v>
@@ -29412,7 +29416,7 @@
         <v>19407.045101398056</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B10" s="20">
         <v>2800</v>
       </c>
@@ -29472,7 +29476,7 @@
         <v>21760.929740325897</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B11" s="20">
         <v>2900</v>
       </c>
@@ -29532,7 +29536,7 @@
         <v>24114.81437925373</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B12" s="14">
         <v>3000</v>
       </c>
@@ -29592,7 +29596,7 @@
         <v>26468.699018181571</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C13" s="16">
         <v>11500</v>
       </c>
@@ -29649,7 +29653,7 @@
         <v>28822.583657109411</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C14" s="16">
         <v>12000</v>
       </c>
@@ -29706,7 +29710,7 @@
         <v>31176.468296037252</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C15" s="16">
         <v>12500</v>
       </c>
@@ -29763,7 +29767,7 @@
         <v>33530.352934965085</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C16" s="16">
         <v>13000</v>
       </c>
@@ -29820,7 +29824,7 @@
         <v>35884.237573892926</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <v>3500</v>
       </c>
@@ -29832,7 +29836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B22" s="16">
         <v>1000</v>
       </c>
@@ -29841,7 +29845,7 @@
         <v>6125000000</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B23" s="16">
         <v>2000</v>
       </c>
@@ -29850,7 +29854,7 @@
         <v>12250000000</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B24" s="16">
         <v>3000</v>
       </c>
@@ -29859,7 +29863,7 @@
         <v>18375000000</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B25" s="16">
         <v>4000</v>
       </c>
@@ -29868,7 +29872,7 @@
         <v>24500000000</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B26" s="16">
         <v>5000</v>
       </c>
@@ -29877,7 +29881,7 @@
         <v>30625000000</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B27" s="16">
         <v>6000</v>
       </c>
@@ -29886,7 +29890,7 @@
         <v>36750000000</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B28" s="16">
         <v>7000</v>
       </c>
@@ -29895,7 +29899,7 @@
         <v>42875000000</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B29" s="16">
         <v>8000</v>
       </c>
@@ -29904,7 +29908,7 @@
         <v>49000000000</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B30" s="16">
         <v>9000</v>
       </c>
@@ -29913,7 +29917,7 @@
         <v>55125000000</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B31" s="16">
         <v>10000</v>
       </c>
@@ -29922,8 +29926,8 @@
         <v>61250000000</v>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="38" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I38" s="25" t="s">
         <v>54</v>
       </c>
@@ -29941,8 +29945,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="I40" s="26" t="s">
         <v>49</v>
       </c>
@@ -29961,7 +29965,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
       <c r="I41" s="12" t="s">
         <v>29</v>
       </c>
@@ -29980,7 +29984,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
       <c r="I42" s="12" t="s">
         <v>30</v>
       </c>
@@ -29999,7 +30003,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
       <c r="I43" s="12" t="s">
         <v>51</v>
       </c>
@@ -30018,12 +30022,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
       <c r="D48" s="72" t="s">
         <v>68</v>
       </c>
@@ -30041,7 +30045,7 @@
       </c>
       <c r="K48" s="72"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D49" s="16" t="s">
         <v>20</v>
       </c>
@@ -30067,7 +30071,7 @@
         <v>4.54</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>65</v>
       </c>
@@ -30103,7 +30107,7 @@
         <v>30000981250</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B51" s="72" t="s">
         <v>69</v>
       </c>
@@ -30133,7 +30137,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>1000</v>
       </c>
@@ -30146,7 +30150,7 @@
       <c r="J52" s="19"/>
       <c r="K52" s="19"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B53">
         <v>125</v>
       </c>
@@ -30187,7 +30191,7 @@
         <v>21.909260599116529</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B54">
         <v>250</v>
       </c>
@@ -30228,7 +30232,7 @@
         <v>15.492186740418539</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B55">
         <v>500</v>
       </c>
@@ -30269,7 +30273,7 @@
         <v>10.954630299558264</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B56">
         <v>1000</v>
       </c>
@@ -30310,7 +30314,7 @@
         <v>7.7460933702092696</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B57">
         <v>2000</v>
       </c>
@@ -30351,7 +30355,7 @@
         <v>5.4773151497791321</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>68</v>
       </c>
@@ -30395,7 +30399,7 @@
         <v>4.9367223600723857</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B59">
         <v>3000</v>
       </c>
@@ -30436,7 +30440,7 @@
         <v>4.4722090924582973</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>49</v>
       </c>
@@ -30480,7 +30484,7 @@
         <v>4.1463887177013214</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>67</v>
       </c>
@@ -30524,7 +30528,7 @@
         <v>3.9223868485583608</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B62">
         <v>4000</v>
       </c>
@@ -30565,7 +30569,7 @@
         <v>3.8730466851046348</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -30609,7 +30613,7 @@
         <v>3.6354217498881027</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B64">
         <v>5000</v>
       </c>
@@ -30650,7 +30654,7 @@
         <v>3.4641582671696742</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65">
         <v>6000</v>
       </c>
@@ -30691,7 +30695,7 @@
         <v>3.1623293761613978</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66">
         <v>7000</v>
       </c>
@@ -30732,7 +30736,7 @@
         <v>2.9277480985514153</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67">
         <v>8000</v>
       </c>
@@ -30773,7 +30777,7 @@
         <v>2.7386575748895661</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68">
         <v>9000</v>
       </c>
@@ -30814,7 +30818,7 @@
         <v>2.5820311234030897</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69">
         <v>10000</v>
       </c>
@@ -30855,7 +30859,7 @@
         <v>2.4495298018191165</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70">
         <v>11000</v>
       </c>
@@ -30896,7 +30900,7 @@
         <v>2.3355350272766975</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71">
         <v>12000</v>
       </c>
@@ -30937,7 +30941,7 @@
         <v>2.2361045462291487</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72">
         <v>13000</v>
       </c>
@@ -30978,7 +30982,7 @@
         <v>2.1483797562170137</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73">
         <v>14000</v>
       </c>
@@ -31019,7 +31023,7 @@
         <v>2.0702305340917264</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74">
         <v>15000</v>
       </c>
@@ -31060,7 +31064,7 @@
         <v>2.0000327080658789</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75">
         <v>16000</v>
       </c>
@@ -31101,7 +31105,7 @@
         <v>1.9365233425523174</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76">
         <v>17000</v>
       </c>
@@ -31142,7 +31146,7 @@
         <v>1.8787035971335002</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77">
         <v>18000</v>
       </c>
@@ -31183,7 +31187,7 @@
         <v>1.8257717165930443</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78">
         <v>19000</v>
       </c>
@@ -31224,7 +31228,7 @@
         <v>1.7770756951564526</v>
       </c>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79">
         <v>20000</v>
       </c>
@@ -31265,7 +31269,7 @@
         <v>1.7320791335848371</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80">
         <v>21000</v>
       </c>
@@ -31306,7 +31310,7 @@
         <v>1.6903361528180747</v>
       </c>
     </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81">
         <v>22000</v>
       </c>
@@ -31347,7 +31351,7 @@
         <v>1.6514726554860608</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82">
         <v>23000</v>
       </c>
@@ -31388,7 +31392,7 @@
         <v>1.6151721203205773</v>
       </c>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83">
         <v>24000</v>
       </c>
@@ -31429,7 +31433,7 @@
         <v>1.5811646880806989</v>
       </c>
     </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84">
         <v>25000</v>
       </c>
@@ -31470,7 +31474,7 @@
         <v>1.5492186740418541</v>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85">
         <v>26000</v>
       </c>
@@ -31511,7 +31515,7 @@
         <v>1.5191338941849526</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86">
         <v>27000</v>
       </c>
@@ -31552,7 +31556,7 @@
         <v>1.4907363641527656</v>
       </c>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B87">
         <v>28000</v>
       </c>
@@ -31593,7 +31597,7 @@
         <v>1.4638740492757076</v>
       </c>
     </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B88">
         <v>29000</v>
       </c>
@@ -31634,7 +31638,7 @@
         <v>1.4384134279320298</v>
       </c>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89">
         <v>30000</v>
       </c>
@@ -31675,7 +31679,7 @@
         <v>1.4142366904682777</v>
       </c>
     </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90">
         <v>31000</v>
       </c>
@@ -31716,7 +31720,7 @@
         <v>1.3912394392840344</v>
       </c>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91">
         <v>32000</v>
       </c>
@@ -31757,7 +31761,7 @@
         <v>1.369328787444783</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92">
         <v>33000</v>
       </c>
@@ -31798,7 +31802,7 @@
         <v>1.3484217767000011</v>
       </c>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93">
         <v>34000</v>
       </c>
@@ -31839,7 +31843,7 @@
         <v>1.3284440533726576</v>
       </c>
     </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94">
         <v>35000</v>
       </c>
@@ -31880,7 +31884,7 @@
         <v>1.3093287538713436</v>
       </c>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B95">
         <v>36000</v>
       </c>
@@ -31921,7 +31925,7 @@
         <v>1.2910155617015449</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96">
         <v>37000</v>
       </c>
@@ -31962,7 +31966,7 @@
         <v>1.273449905635146</v>
       </c>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97">
         <v>38000</v>
       </c>
@@ -32003,7 +32007,7 @@
         <v>1.2565822747269255</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B98">
         <v>39000</v>
       </c>
@@ -32044,7 +32048,7 @@
         <v>1.2403676305734357</v>
       </c>
     </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99">
         <v>40000</v>
       </c>
@@ -32085,7 +32089,7 @@
         <v>1.2247649009095583</v>
       </c>
     </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B100">
         <v>41000</v>
       </c>
@@ -32126,7 +32130,7 @@
         <v>1.2097365415659727</v>
       </c>
     </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101">
         <v>42000</v>
       </c>
@@ -32167,7 +32171,7 @@
         <v>1.1952481561424408</v>
       </c>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B102">
         <v>43000</v>
       </c>
@@ -32208,7 +32212,7 @@
         <v>1.1812681646197811</v>
       </c>
     </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103">
         <v>44000</v>
       </c>
@@ -32249,7 +32253,7 @@
         <v>1.1677675136383487</v>
       </c>
     </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B104">
         <v>45000</v>
       </c>
@@ -32290,7 +32294,7 @@
         <v>1.1547194223898913</v>
       </c>
     </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105">
         <v>46000</v>
       </c>
@@ -32331,7 +32335,7 @@
         <v>1.1420991590621346</v>
       </c>
     </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B106">
         <v>47000</v>
       </c>
@@ -32372,7 +32376,7 @@
         <v>1.1298838435874725</v>
       </c>
     </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107">
         <v>48000</v>
       </c>
@@ -32413,7 +32417,7 @@
         <v>1.1180522731145743</v>
       </c>
     </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108">
         <v>49000</v>
       </c>
@@ -32454,7 +32458,7 @@
         <v>1.1065847671727529</v>
       </c>
     </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B109">
         <v>50000</v>
       </c>
@@ -32495,7 +32499,7 @@
         <v>1.0954630299558263</v>
       </c>
     </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B110">
         <v>51000</v>
       </c>
@@ -32536,7 +32540,7 @@
         <v>1.0846700275325445</v>
       </c>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B111">
         <v>52000</v>
       </c>
@@ -32577,7 +32581,7 @@
         <v>1.0741898781085069</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112">
         <v>53000</v>
       </c>
@@ -32618,7 +32622,7 @@
         <v>1.0640077537311465</v>
       </c>
     </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113">
         <v>54000</v>
       </c>
@@ -32659,7 +32663,7 @@
         <v>1.0541097920537992</v>
       </c>
     </row>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114">
         <v>55000</v>
       </c>
@@ -32700,7 +32704,7 @@
         <v>1.0444830169645043</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115">
         <v>56000</v>
       </c>
@@ -32741,7 +32745,7 @@
         <v>1.0351152670458632</v>
       </c>
     </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116">
         <v>57000</v>
       </c>
@@ -32782,7 +32786,7 @@
         <v>1.0259951309689193</v>
       </c>
     </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117">
         <v>58000</v>
       </c>
@@ -32823,7 +32827,7 @@
         <v>1.0171118890405255</v>
       </c>
     </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B118">
         <v>59000</v>
       </c>
@@ -32864,7 +32868,7 @@
         <v>1.0084554602233244</v>
       </c>
     </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B119">
         <v>60000</v>
       </c>
@@ -32905,7 +32909,7 @@
         <v>1.0000163540329394</v>
       </c>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B120">
         <v>61000</v>
       </c>
@@ -32946,7 +32950,7 @@
         <v>0.99178562679048565</v>
       </c>
     </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B121">
         <v>62000</v>
       </c>
@@ -32987,7 +32991,7 @@
         <v>0.98375484177191097</v>
       </c>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B122">
         <v>63000</v>
       </c>
@@ -33028,7 +33032,7 @@
         <v>0.97591603285047179</v>
       </c>
     </row>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B123">
         <v>64000</v>
       </c>
@@ -33069,7 +33073,7 @@
         <v>0.9682616712761587</v>
       </c>
     </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B124">
         <v>65000</v>
       </c>
@@ -33110,7 +33114,7 @@
         <v>0.96078463527713398</v>
       </c>
     </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B125">
         <v>66000</v>
       </c>
@@ -33151,7 +33155,7 @@
         <v>0.95347818220418334</v>
       </c>
     </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B126">
         <v>67000</v>
       </c>
@@ -33192,7 +33196,7 @@
         <v>0.94633592297052627</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127">
         <v>68000</v>
       </c>
@@ -33233,7 +33237,7 @@
         <v>0.93935179856675011</v>
       </c>
     </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B128">
         <v>69000</v>
       </c>
@@ -33274,7 +33278,7 @@
         <v>0.93252005845466401</v>
       </c>
     </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B129">
         <v>70000</v>
       </c>
@@ -33315,7 +33319,7 @@
         <v>0.92583524066495915</v>
       </c>
     </row>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B130">
         <v>71000</v>
       </c>
@@ -33356,7 +33360,7 @@
         <v>0.91929215344213711</v>
       </c>
     </row>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B131">
         <v>72000</v>
       </c>
@@ -33397,7 +33401,7 @@
         <v>0.91288585829652213</v>
       </c>
     </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B132">
         <v>73000</v>
       </c>
@@ -33438,7 +33442,7 @@
         <v>0.90661165433763413</v>
       </c>
     </row>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B133">
         <v>74000</v>
       </c>
@@ -33479,7 +33483,7 @@
         <v>0.90046506377598079</v>
       </c>
     </row>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B134">
         <v>75000</v>
       </c>
@@ -33520,7 +33524,7 @@
         <v>0.89444181849165938</v>
       </c>
     </row>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B135">
         <v>76000</v>
       </c>
@@ -33561,7 +33565,7 @@
         <v>0.88853784757822629</v>
       </c>
     </row>
-    <row r="136" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B136">
         <v>77000</v>
       </c>
@@ -33602,7 +33606,7 @@
         <v>0.88274926577922808</v>
       </c>
     </row>
-    <row r="137" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B137">
         <v>78000</v>
       </c>
@@ -33643,7 +33647,7 @@
         <v>0.87707236274276679</v>
       </c>
     </row>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B138">
         <v>79000</v>
       </c>
@@ -33684,7 +33688,7 @@
         <v>0.87150359302657376</v>
       </c>
     </row>
-    <row r="139" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B139">
         <v>80000</v>
       </c>
@@ -33725,7 +33729,7 @@
         <v>0.86603956679241856</v>
       </c>
     </row>
-    <row r="140" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B140">
         <v>81000</v>
       </c>
@@ -33766,7 +33770,7 @@
         <v>0.86067704113436327</v>
       </c>
     </row>
-    <row r="141" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B141">
         <v>82000</v>
       </c>
@@ -33807,7 +33811,7 @@
         <v>0.85541291199046088</v>
       </c>
     </row>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B142">
         <v>83000</v>
       </c>
@@ -33848,7 +33852,7 @@
         <v>0.8502442065920669</v>
       </c>
     </row>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B143">
         <v>84000</v>
       </c>
@@ -33889,7 +33893,7 @@
         <v>0.84516807640903735</v>
       </c>
     </row>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B144">
         <v>85000</v>
       </c>
@@ -33930,7 +33934,7 @@
         <v>0.84018179055277709</v>
       </c>
     </row>
-    <row r="145" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B145">
         <v>86000</v>
       </c>
@@ -33971,7 +33975,7 @@
         <v>0.8352827296024341</v>
       </c>
     </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B146">
         <v>87000</v>
       </c>
@@ -34012,7 +34016,7 @@
         <v>0.83046837982252963</v>
       </c>
     </row>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B147">
         <v>88000</v>
       </c>
@@ -34053,7 +34057,7 @@
         <v>0.82573632774303041</v>
       </c>
     </row>
-    <row r="148" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B148">
         <v>89000</v>
       </c>
@@ -34094,7 +34098,7 @@
         <v>0.82108425507531457</v>
       </c>
     </row>
-    <row r="149" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B149">
         <v>90000</v>
       </c>
@@ -34135,7 +34139,7 @@
         <v>0.8165099339397055</v>
       </c>
     </row>
-    <row r="150" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B150">
         <v>91000</v>
       </c>
@@ -34176,7 +34180,7 @@
         <v>0.81201122238225587</v>
       </c>
     </row>
-    <row r="151" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B151">
         <v>92000</v>
       </c>
@@ -34217,7 +34221,7 @@
         <v>0.80758606016028867</v>
       </c>
     </row>
-    <row r="152" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B152">
         <v>93000</v>
       </c>
@@ -34258,7 +34262,7 @@
         <v>0.80323246477786125</v>
       </c>
     </row>
-    <row r="153" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B153">
         <v>94000</v>
       </c>
@@ -34299,7 +34303,7 @@
         <v>0.79894852775382219</v>
       </c>
     </row>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B154">
         <v>95000</v>
       </c>
@@ -34340,7 +34344,7 @@
         <v>0.79473241110650439</v>
       </c>
     </row>
-    <row r="155" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B155">
         <v>96000</v>
       </c>
@@ -34381,7 +34385,7 @@
         <v>0.79058234404034944</v>
       </c>
     </row>
-    <row r="156" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B156">
         <v>97000</v>
       </c>
@@ -34422,7 +34426,7 @@
         <v>0.78649661982089325</v>
       </c>
     </row>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B157">
         <v>98000</v>
       </c>
@@ -34463,7 +34467,7 @@
         <v>0.78247359282559037</v>
       </c>
     </row>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B158">
         <v>99000</v>
       </c>
@@ -34504,7 +34508,7 @@
         <v>0.77851167575889901</v>
       </c>
     </row>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B159">
         <v>100000</v>
       </c>
@@ -34545,7 +34549,7 @@
         <v>0.77460933702092705</v>
       </c>
     </row>
-    <row r="160" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B160">
         <v>101000</v>
       </c>
@@ -34586,7 +34590,7 @@
         <v>0.77076509821972572</v>
       </c>
     </row>
-    <row r="161" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B161">
         <v>102000</v>
       </c>
@@ -34627,7 +34631,7 @@
         <v>0.7669775318180615</v>
       </c>
     </row>
-    <row r="162" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B162">
         <v>103000</v>
       </c>
@@ -34668,7 +34672,7 @@
         <v>0.76324525890615169</v>
       </c>
     </row>
-    <row r="163" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B163">
         <v>104000</v>
       </c>
@@ -34709,7 +34713,7 @@
         <v>0.7595669470924763</v>
       </c>
     </row>
-    <row r="164" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B164">
         <v>105000</v>
       </c>
@@ -34750,7 +34754,7 @@
         <v>0.75594130850533758</v>
       </c>
     </row>
-    <row r="165" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B165">
         <v>106000</v>
       </c>
@@ -34791,7 +34795,7 @@
         <v>0.75236709789835965</v>
       </c>
     </row>
-    <row r="166" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B166">
         <v>107000</v>
       </c>
@@ -34832,7 +34836,7 @@
         <v>0.7488431108536</v>
       </c>
     </row>
-    <row r="167" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B167">
         <v>108000</v>
       </c>
@@ -34873,7 +34877,7 @@
         <v>0.74536818207638278</v>
       </c>
     </row>
-    <row r="168" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B168">
         <v>109000</v>
       </c>
@@ -34914,7 +34918,7 @@
         <v>0.7419411837763733</v>
       </c>
     </row>
-    <row r="169" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B169">
         <v>110000</v>
       </c>
@@ -34955,7 +34959,7 @@
         <v>0.73856102412978464</v>
       </c>
     </row>
-    <row r="170" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B170">
         <v>111000</v>
       </c>
@@ -34996,7 +35000,7 @@
         <v>0.73522664581795505</v>
       </c>
     </row>
-    <row r="171" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B171">
         <v>112000</v>
       </c>
@@ -35037,7 +35041,7 @@
         <v>0.73193702463785382</v>
       </c>
     </row>
-    <row r="172" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B172">
         <v>113000</v>
       </c>
@@ -35078,7 +35082,7 @@
         <v>0.72869116818036905</v>
       </c>
     </row>
-    <row r="173" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B173">
         <v>114000</v>
       </c>
@@ -35119,7 +35123,7 @@
         <v>0.72548811457250284</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174">
         <v>115000</v>
       </c>
@@ -35160,7 +35164,7 @@
         <v>0.72232693127985603</v>
       </c>
     </row>
-    <row r="175" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B175">
         <v>116000</v>
       </c>
@@ -35201,7 +35205,7 @@
         <v>0.71920671396601488</v>
       </c>
     </row>
-    <row r="176" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B176">
         <v>117000</v>
       </c>
@@ -35242,7 +35246,7 @@
         <v>0.71612658540567131</v>
       </c>
     </row>
-    <row r="177" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B177">
         <v>118000</v>
       </c>
@@ -35283,7 +35287,7 @@
         <v>0.71308569444851344</v>
       </c>
     </row>
-    <row r="178" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B178">
         <v>119000</v>
       </c>
@@ -35324,7 +35328,7 @@
         <v>0.71008321503110294</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179">
         <v>120000</v>
       </c>
@@ -35365,7 +35369,7 @@
         <v>0.70711834523413886</v>
       </c>
     </row>
-    <row r="180" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B180">
         <v>121000</v>
       </c>
@@ -35406,7 +35410,7 @@
         <v>0.70419030638266089</v>
       </c>
     </row>
-    <row r="181" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B181">
         <v>122000</v>
       </c>
@@ -35447,7 +35451,7 @@
         <v>0.7012983421869029</v>
       </c>
     </row>
-    <row r="182" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B182">
         <v>123000</v>
       </c>
@@ -35488,7 +35492,7 @@
         <v>0.69844171792164111</v>
       </c>
     </row>
-    <row r="183" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B183">
         <v>124000</v>
       </c>
@@ -35529,7 +35533,7 @@
         <v>0.69561971964201719</v>
       </c>
     </row>
-    <row r="184" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B184">
         <v>125000</v>
       </c>
@@ -35570,7 +35574,7 @@
         <v>0.69283165343393494</v>
       </c>
     </row>
-    <row r="185" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B185">
         <v>126000</v>
       </c>
@@ -35611,7 +35615,7 @@
         <v>0.69007684469724206</v>
       </c>
     </row>
-    <row r="186" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B186">
         <v>127000</v>
       </c>
@@ -35652,7 +35656,7 @@
         <v>0.68735463746001979</v>
       </c>
     </row>
-    <row r="187" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B187">
         <v>128000</v>
       </c>
@@ -35693,7 +35697,7 @@
         <v>0.68466439372239152</v>
       </c>
     </row>
-    <row r="188" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B188">
         <v>129000</v>
       </c>
@@ -35734,7 +35738,7 @@
         <v>0.68200549282836576</v>
       </c>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B189">
         <v>130000</v>
       </c>
@@ -35775,7 +35779,7 @@
         <v>0.67937733086430518</v>
       </c>
     </row>
-    <row r="190" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B190">
         <v>131000</v>
       </c>
@@ -35816,7 +35820,7 @@
         <v>0.67677932008270103</v>
       </c>
     </row>
-    <row r="191" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B191">
         <v>132000</v>
       </c>
@@ -35857,7 +35861,7 @@
         <v>0.67421088835000054</v>
       </c>
     </row>
-    <row r="192" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B192">
         <v>133000</v>
       </c>
@@ -35898,7 +35902,7 @@
         <v>0.67167147861731469</v>
       </c>
     </row>
-    <row r="193" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B193">
         <v>134000</v>
       </c>
@@ -35939,7 +35943,7 @@
         <v>0.6691605484128893</v>
       </c>
     </row>
-    <row r="194" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B194">
         <v>135000</v>
       </c>
@@ -35980,7 +35984,7 @@
         <v>0.66667756935529288</v>
       </c>
     </row>
-    <row r="195" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B195">
         <v>136000</v>
       </c>
@@ -36021,7 +36025,7 @@
         <v>0.66422202668632879</v>
       </c>
     </row>
-    <row r="196" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B196">
         <v>137000</v>
       </c>
@@ -36062,7 +36066,7 @@
         <v>0.66179341882273224</v>
       </c>
     </row>
-    <row r="197" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B197">
         <v>138000</v>
       </c>
@@ -36103,7 +36107,7 @@
         <v>0.6593912569257685</v>
       </c>
     </row>
-    <row r="198" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B198">
         <v>139000</v>
       </c>
@@ -36144,7 +36148,7 @@
         <v>0.65701506448789193</v>
       </c>
     </row>
-    <row r="199" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B199">
         <v>140000</v>
       </c>
@@ -36185,7 +36189,7 @@
         <v>0.65466437693567181</v>
       </c>
     </row>
-    <row r="200" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B200">
         <v>141000</v>
       </c>
@@ -36226,7 +36230,7 @@
         <v>0.65233874124823621</v>
       </c>
     </row>
-    <row r="201" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B201">
         <v>142000</v>
       </c>
@@ -36267,7 +36271,7 @@
         <v>0.65003771559051926</v>
       </c>
     </row>
-    <row r="202" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B202">
         <v>143000</v>
       </c>
@@ -36308,7 +36312,7 @@
         <v>0.64776086896064</v>
       </c>
     </row>
-    <row r="203" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B203">
         <v>144000</v>
       </c>
@@ -36349,7 +36353,7 @@
         <v>0.64550778085077243</v>
       </c>
     </row>
-    <row r="204" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B204">
         <v>145000</v>
       </c>
@@ -36390,7 +36394,7 @@
         <v>0.64327804092090268</v>
       </c>
     </row>
-    <row r="205" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B205">
         <v>146000</v>
       </c>
@@ -36431,7 +36435,7 @@
         <v>0.6410712486848954</v>
       </c>
     </row>
-    <row r="206" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B206">
         <v>147000</v>
       </c>
@@ -36472,7 +36476,7 @@
         <v>0.63888701320832819</v>
       </c>
     </row>
-    <row r="207" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B207">
         <v>148000</v>
       </c>
@@ -36513,7 +36517,7 @@
         <v>0.63672495281757302</v>
       </c>
     </row>
-    <row r="208" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B208">
         <v>149000</v>
       </c>
@@ -36554,7 +36558,7 @@
         <v>0.63458469481963475</v>
       </c>
     </row>
-    <row r="209" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B209">
         <v>150000</v>
       </c>
@@ -36595,7 +36599,7 @@
         <v>0.63246587523227948</v>
       </c>
     </row>
-    <row r="210" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B210">
         <v>151000</v>
       </c>
@@ -36636,7 +36640,7 @@
         <v>0.63036813852400975</v>
       </c>
     </row>
-    <row r="211" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B211">
         <v>152000</v>
       </c>
@@ -36677,7 +36681,7 @@
         <v>0.62829113736346276</v>
       </c>
     </row>
-    <row r="212" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B212">
         <v>153000</v>
       </c>
@@ -36718,7 +36722,7 @@
         <v>0.62623453237783333</v>
       </c>
     </row>
-    <row r="213" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B213">
         <v>154000</v>
       </c>
@@ -36759,7 +36763,7 @@
         <v>0.62419799191993808</v>
       </c>
     </row>
-    <row r="214" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B214">
         <v>155000</v>
       </c>
@@ -36800,7 +36804,7 @@
         <v>0.62218119184355847</v>
       </c>
     </row>
-    <row r="215" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B215">
         <v>156000</v>
       </c>
@@ -36841,7 +36845,7 @@
         <v>0.62018381528671784</v>
       </c>
     </row>
-    <row r="216" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B216">
         <v>157000</v>
       </c>
@@ -36882,7 +36886,7 @@
         <v>0.61820555246256192</v>
       </c>
     </row>
-    <row r="217" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B217">
         <v>158000</v>
       </c>
@@ -36923,7 +36927,7 @@
         <v>0.61624610045753137</v>
       </c>
     </row>
-    <row r="218" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B218">
         <v>159000</v>
       </c>
@@ -36964,7 +36968,7 @@
         <v>0.61430516303652649</v>
       </c>
     </row>
-    <row r="219" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B219">
         <v>160000</v>
       </c>
@@ -37005,7 +37009,7 @@
         <v>0.61238245045477913</v>
       </c>
     </row>
-    <row r="220" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B220">
         <v>161000</v>
       </c>
@@ -37046,7 +37050,7 @@
         <v>0.61047767927616314</v>
       </c>
     </row>
-    <row r="221" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B221">
         <v>162000</v>
       </c>
@@ -37087,7 +37091,7 @@
         <v>0.60859057219768131</v>
       </c>
     </row>
-    <row r="222" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B222">
         <v>163000</v>
       </c>
@@ -37128,7 +37132,7 @@
         <v>0.6067208578798845</v>
       </c>
     </row>
-    <row r="223" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B223">
         <v>164000</v>
       </c>
@@ -37169,7 +37173,7 @@
         <v>0.60486827078298633</v>
       </c>
     </row>
-    <row r="224" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B224">
         <v>165000</v>
       </c>
@@ -37210,7 +37214,7 @@
         <v>0.60303255100844899</v>
       </c>
     </row>
-    <row r="225" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B225">
         <v>166000</v>
       </c>
@@ -37251,7 +37255,7 @@
         <v>0.60121344414582645</v>
       </c>
     </row>
-    <row r="226" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B226">
         <v>167000</v>
       </c>
@@ -37292,7 +37296,7 @@
         <v>0.59941070112465833</v>
       </c>
     </row>
-    <row r="227" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B227">
         <v>168000</v>
       </c>
@@ -37333,7 +37337,7 @@
         <v>0.59762407807122042</v>
       </c>
     </row>
-    <row r="228" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B228">
         <v>169000</v>
       </c>
@@ -37374,7 +37378,7 @@
         <v>0.59585333616994385</v>
       </c>
     </row>
-    <row r="229" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B229">
         <v>170000</v>
       </c>
@@ -37415,7 +37419,7 @@
         <v>0.59409824152932422</v>
       </c>
     </row>
-    <row r="230" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B230">
         <v>171000</v>
       </c>
@@ -37456,7 +37460,7 @@
         <v>0.5923585650521509</v>
       </c>
     </row>
-    <row r="231" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B231">
         <v>172000</v>
       </c>
@@ -37497,7 +37501,7 @@
         <v>0.59063408230989056</v>
       </c>
     </row>
-    <row r="232" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B232">
         <v>173000</v>
       </c>
@@ -37538,7 +37542,7 @@
         <v>0.5889245734210713</v>
       </c>
     </row>
-    <row r="233" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B233">
         <v>174000</v>
       </c>
@@ -37579,7 +37583,7 @@
         <v>0.58722982293351622</v>
       </c>
     </row>
-    <row r="234" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B234">
         <v>175000</v>
       </c>
@@ -37620,7 +37624,7 @@
         <v>0.58554961971028308</v>
       </c>
     </row>
-    <row r="235" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B235">
         <v>176000</v>
       </c>
@@ -37661,7 +37665,7 @@
         <v>0.58388375681917437</v>
       </c>
     </row>
-    <row r="236" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B236">
         <v>177000</v>
       </c>
@@ -37702,7 +37706,7 @@
         <v>0.58223203142568436</v>
       </c>
     </row>
-    <row r="237" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B237">
         <v>178000</v>
       </c>
@@ -37743,7 +37747,7 @@
         <v>0.58059424468925991</v>
       </c>
     </row>
-    <row r="238" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B238">
         <v>179000</v>
       </c>
@@ -37784,7 +37788,7 @@
         <v>0.57897020166275204</v>
       </c>
     </row>
-    <row r="239" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B239">
         <v>180000</v>
       </c>
@@ -37825,7 +37829,7 @@
         <v>0.57735971119494567</v>
       </c>
     </row>
-    <row r="240" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B240">
         <v>181000</v>
       </c>
@@ -37866,7 +37870,7 @@
         <v>0.57576258583605344</v>
       </c>
     </row>
-    <row r="241" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B241">
         <v>182000</v>
       </c>
@@ -37907,7 +37911,7 @@
         <v>0.57417864174607081</v>
       </c>
     </row>
-    <row r="242" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B242">
         <v>183000</v>
       </c>
@@ -37948,7 +37952,7 @@
         <v>0.57260769860588867</v>
       </c>
     </row>
-    <row r="243" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B243">
         <v>184000</v>
       </c>
@@ -37989,7 +37993,7 @@
         <v>0.57104957953106728</v>
       </c>
     </row>
-    <row r="244" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B244">
         <v>185000</v>
       </c>
@@ -38030,7 +38034,7 @@
         <v>0.56950411098817577</v>
       </c>
     </row>
-    <row r="245" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B245">
         <v>186000</v>
       </c>
@@ -38071,7 +38075,7 @@
         <v>0.5679711227136105</v>
       </c>
     </row>
-    <row r="246" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B246">
         <v>187000</v>
       </c>
@@ -38112,7 +38116,7 @@
         <v>0.56645044763480279</v>
       </c>
     </row>
-    <row r="247" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B247">
         <v>188000</v>
       </c>
@@ -38153,7 +38157,7 @@
         <v>0.56494192179373626</v>
       </c>
     </row>
-    <row r="248" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B248">
         <v>189000</v>
       </c>
@@ -38194,7 +38198,7 @@
         <v>0.56344538427269164</v>
       </c>
     </row>
-    <row r="249" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B249">
         <v>190000</v>
       </c>
@@ -38235,7 +38239,7 @@
         <v>0.56196067712214426</v>
       </c>
     </row>
-    <row r="250" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B250">
         <v>191000</v>
       </c>
@@ -38276,7 +38280,7 @@
         <v>0.56048764529074158</v>
       </c>
     </row>
-    <row r="251" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B251">
         <v>192000</v>
       </c>
@@ -38317,7 +38321,7 @@
         <v>0.55902613655728717</v>
       </c>
     </row>
-    <row r="252" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B252">
         <v>193000</v>
       </c>
@@ -38358,7 +38362,7 @@
         <v>0.55757600146466713</v>
       </c>
     </row>
-    <row r="253" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B253">
         <v>194000</v>
       </c>
@@ -38399,7 +38403,7 @@
         <v>0.55613709325565164</v>
       </c>
     </row>
-    <row r="254" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B254">
         <v>195000</v>
       </c>
@@ -38440,7 +38444,7 @@
         <v>0.55470926781050967</v>
       </c>
     </row>
-    <row r="255" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B255">
         <v>196000</v>
       </c>
@@ -38481,7 +38485,7 @@
         <v>0.55329238358637645</v>
       </c>
     </row>
-    <row r="256" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B256">
         <v>197000</v>
       </c>
@@ -38522,7 +38526,7 @@
         <v>0.55188630155831531</v>
       </c>
     </row>
-    <row r="257" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B257">
         <v>198000</v>
       </c>
@@ -38563,7 +38567,7 @@
         <v>0.55049088516202027</v>
       </c>
     </row>
-    <row r="258" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B258">
         <v>199000</v>
       </c>
@@ -38604,7 +38608,7 @@
         <v>0.54910600023810285</v>
       </c>
     </row>
-    <row r="259" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B259">
         <v>200000</v>
       </c>
@@ -38645,7 +38649,7 @@
         <v>0.54773151497791317</v>
       </c>
     </row>
-    <row r="260" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B260">
         <v>201000</v>
       </c>
@@ -38686,7 +38690,7 @@
         <v>0.54636729987084631</v>
       </c>
     </row>
-    <row r="261" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B261">
         <v>202000</v>
       </c>
@@ -38727,7 +38731,7 @@
         <v>0.54501322765308335</v>
       </c>
     </row>
-    <row r="262" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B262">
         <v>203000</v>
       </c>
@@ -38768,7 +38772,7 @@
         <v>0.54366917325772568</v>
       </c>
     </row>
-    <row r="263" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B263">
         <v>204000</v>
       </c>
@@ -38809,7 +38813,7 @@
         <v>0.54233501376627224</v>
       </c>
     </row>
-    <row r="264" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B264">
         <v>205000</v>
       </c>
@@ -38850,7 +38854,7 @@
         <v>0.5410106283614029</v>
       </c>
     </row>
-    <row r="265" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B265">
         <v>206000</v>
       </c>
@@ -38891,7 +38895,7 @@
         <v>0.53969589828102194</v>
       </c>
     </row>
-    <row r="266" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B266">
         <v>207000</v>
       </c>
@@ -38932,7 +38936,7 @@
         <v>0.53839070677352574</v>
       </c>
     </row>
-    <row r="267" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B267">
         <v>208000</v>
       </c>
@@ -38973,7 +38977,7 @@
         <v>0.53709493905425343</v>
       </c>
     </row>
-    <row r="268" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B268">
         <v>209000</v>
       </c>
@@ -39014,7 +39018,7 @@
         <v>0.53580848226308608</v>
       </c>
     </row>
-    <row r="269" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B269">
         <v>210000</v>
       </c>
@@ -39055,7 +39059,7 @@
         <v>0.53453122542315612</v>
       </c>
     </row>
-    <row r="270" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B270">
         <v>211000</v>
       </c>
@@ -39096,7 +39100,7 @@
         <v>0.53326305940063679</v>
       </c>
     </row>
-    <row r="271" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B271">
         <v>212000</v>
       </c>
@@ -39137,7 +39141,7 @@
         <v>0.53200387686557327</v>
       </c>
     </row>
-    <row r="272" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B272">
         <v>213000</v>
       </c>
@@ -39178,7 +39182,7 @@
         <v>0.53075357225372866</v>
       </c>
     </row>
-    <row r="273" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B273">
         <v>214000</v>
       </c>
@@ -39219,7 +39223,7 @@
         <v>0.52951204172941013</v>
       </c>
     </row>
-    <row r="274" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B274">
         <v>215000</v>
       </c>
@@ -39260,7 +39264,7 @@
         <v>0.52827918314924838</v>
       </c>
     </row>
-    <row r="275" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B275">
         <v>216000</v>
       </c>
@@ -39301,7 +39305,7 @@
         <v>0.52705489602689959</v>
       </c>
     </row>
-    <row r="276" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B276">
         <v>217000</v>
       </c>
@@ -39342,7 +39346,7 @@
         <v>0.52583908149864289</v>
       </c>
     </row>
-    <row r="277" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B277">
         <v>218000</v>
       </c>
@@ -39383,7 +39387,7 @@
         <v>0.52463164228984804</v>
       </c>
     </row>
-    <row r="278" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B278">
         <v>219000</v>
       </c>
@@ -39424,7 +39428,7 @@
         <v>0.52343248268228515</v>
       </c>
     </row>
-    <row r="279" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B279">
         <v>220000</v>
       </c>
@@ -39465,7 +39469,7 @@
         <v>0.52224150848225215</v>
       </c>
     </row>
-    <row r="280" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B280">
         <v>221000</v>
       </c>
@@ -39506,7 +39510,7 @@
         <v>0.52105862698949823</v>
       </c>
     </row>
-    <row r="281" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B281">
         <v>222000</v>
       </c>
@@ -39547,7 +39551,7 @@
         <v>0.51988374696691597</v>
       </c>
     </row>
-    <row r="282" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B282">
         <v>223000</v>
       </c>
@@ -39588,7 +39592,7 @@
         <v>0.51871677861098353</v>
       </c>
     </row>
-    <row r="283" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B283">
         <v>224000</v>
       </c>
@@ -39629,7 +39633,7 @@
         <v>0.5175576335229316</v>
       </c>
     </row>
-    <row r="284" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B284">
         <v>225000</v>
       </c>
@@ -39670,7 +39674,7 @@
         <v>0.51640622468061792</v>
       </c>
     </row>
-    <row r="285" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B285">
         <v>226000</v>
       </c>
@@ -39711,7 +39715,7 @@
         <v>0.51526246641108586</v>
       </c>
     </row>
-    <row r="286" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B286">
         <v>227000</v>
       </c>
@@ -39752,7 +39756,7 @@
         <v>0.51412627436378844</v>
       </c>
     </row>
-    <row r="287" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B287">
         <v>228000</v>
       </c>
@@ -39793,7 +39797,7 @@
         <v>0.51299756548445963</v>
       </c>
     </row>
-    <row r="288" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B288">
         <v>229000</v>
       </c>
@@ -39834,7 +39838,7 @@
         <v>0.51187625798961389</v>
       </c>
     </row>
-    <row r="289" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B289">
         <v>230000</v>
       </c>
@@ -39875,7 +39879,7 @@
         <v>0.51076227134165553</v>
       </c>
     </row>
-    <row r="290" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B290">
         <v>231000</v>
       </c>
@@ -39916,7 +39920,7 @@
         <v>0.50965552622458177</v>
       </c>
     </row>
-    <row r="291" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B291">
         <v>232000</v>
       </c>
@@ -39957,7 +39961,7 @@
         <v>0.50855594452026276</v>
       </c>
     </row>
-    <row r="292" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B292">
         <v>233000</v>
       </c>
@@ -39998,7 +40002,7 @@
         <v>0.50746344928528109</v>
       </c>
     </row>
-    <row r="293" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B293">
         <v>234000</v>
       </c>
@@ -40039,7 +40043,7 @@
         <v>0.50637796472831753</v>
       </c>
     </row>
-    <row r="294" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B294">
         <v>235000</v>
       </c>
@@ -40080,7 +40084,7 @@
         <v>0.50529941618806562</v>
       </c>
     </row>
-    <row r="295" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B295">
         <v>236000</v>
       </c>
@@ -40121,7 +40125,7 @@
         <v>0.50422773011166222</v>
       </c>
     </row>
-    <row r="296" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B296">
         <v>237000</v>
       </c>
@@ -40162,7 +40166,7 @@
         <v>0.50316283403361839</v>
       </c>
     </row>
-    <row r="297" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B297">
         <v>238000</v>
       </c>
@@ -40203,7 +40207,7 @@
         <v>0.50210465655523828</v>
       </c>
     </row>
-    <row r="298" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B298">
         <v>239000</v>
       </c>
@@ -40244,7 +40248,7 @@
         <v>0.50105312732451202</v>
       </c>
     </row>
-    <row r="299" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B299">
         <v>240000</v>
       </c>
@@ -40285,7 +40289,7 @@
         <v>0.50000817701646971</v>
       </c>
     </row>
-    <row r="300" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B300">
         <v>241000</v>
       </c>
@@ -40326,7 +40330,7 @@
         <v>0.49896973731398453</v>
       </c>
     </row>
-    <row r="301" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B301">
         <v>242000</v>
       </c>
@@ -40367,7 +40371,7 @@
         <v>0.49793774088901205</v>
       </c>
     </row>
-    <row r="302" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B302">
         <v>243000</v>
       </c>
@@ -40408,7 +40412,7 @@
         <v>0.49691212138425528</v>
       </c>
     </row>
-    <row r="303" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B303">
         <v>244000</v>
       </c>
@@ -40449,7 +40453,7 @@
         <v>0.49589281339524283</v>
       </c>
     </row>
-    <row r="304" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B304">
         <v>245000</v>
       </c>
@@ -40490,7 +40494,7 @@
         <v>0.49487975245281057</v>
       </c>
     </row>
-    <row r="305" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B305">
         <v>246000</v>
       </c>
@@ -40531,7 +40535,7 @@
         <v>0.49387287500597427</v>
       </c>
     </row>
-    <row r="306" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B306">
         <v>247000</v>
       </c>
@@ -40572,7 +40576,7 @@
         <v>0.49287211840518491</v>
       </c>
     </row>
-    <row r="307" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B307">
         <v>248000</v>
       </c>
@@ -40613,7 +40617,7 @@
         <v>0.49187742088595549</v>
       </c>
     </row>
-    <row r="308" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B308">
         <v>249000</v>
       </c>
@@ -40654,7 +40658,7 @@
         <v>0.49088872155284963</v>
       </c>
     </row>
-    <row r="309" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B309">
         <v>250000</v>
       </c>
@@ -40695,7 +40699,7 @@
         <v>0.48990596036382328</v>
       </c>
     </row>
-    <row r="310" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B310">
         <v>251000</v>
       </c>
@@ -40736,7 +40740,7 @@
         <v>0.48892907811490904</v>
       </c>
     </row>
-    <row r="311" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B311">
         <v>252000</v>
       </c>
@@ -40777,7 +40781,7 @@
         <v>0.4879580164252359</v>
       </c>
     </row>
-    <row r="312" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B312">
         <v>253000</v>
       </c>
@@ -40818,7 +40822,7 @@
         <v>0.48699271772237468</v>
       </c>
     </row>
-    <row r="313" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B313">
         <v>254000</v>
       </c>
@@ -40859,7 +40863,7 @@
         <v>0.48603312522800091</v>
       </c>
     </row>
-    <row r="314" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B314">
         <v>255000</v>
       </c>
@@ -40900,7 +40904,7 @@
         <v>0.48507918294386765</v>
       </c>
     </row>
-    <row r="315" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B315">
         <v>256000</v>
       </c>
@@ -40941,7 +40945,7 @@
         <v>0.48413083563807935</v>
       </c>
     </row>
-    <row r="316" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B316">
         <v>257000</v>
       </c>
@@ -40982,7 +40986,7 @@
         <v>0.48318802883166057</v>
       </c>
     </row>
-    <row r="317" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B317">
         <v>258000</v>
       </c>
@@ -41023,7 +41027,7 @@
         <v>0.48225070878541071</v>
       </c>
     </row>
-    <row r="318" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B318">
         <v>259000</v>
       </c>
@@ -41064,7 +41068,7 @@
         <v>0.48131882248703806</v>
       </c>
     </row>
-    <row r="319" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B319">
         <v>260000</v>
       </c>
@@ -41105,7 +41109,7 @@
         <v>0.48039231763856699</v>
       </c>
     </row>
-    <row r="320" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B320">
         <v>261000</v>
       </c>
@@ -41146,7 +41150,7 @@
         <v>0.47947114264400986</v>
       </c>
     </row>
-    <row r="321" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B321">
         <v>262000</v>
       </c>
@@ -41187,7 +41191,7 @@
         <v>0.47855524659729887</v>
       </c>
     </row>
-    <row r="322" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B322">
         <v>263000</v>
       </c>
@@ -41228,7 +41232,7 @@
         <v>0.4776445792704696</v>
       </c>
     </row>
-    <row r="323" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B323">
         <v>264000</v>
       </c>
@@ -41269,7 +41273,7 @@
         <v>0.47673909110209167</v>
       </c>
     </row>
-    <row r="324" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B324">
         <v>265000</v>
       </c>
@@ -41310,7 +41314,7 @@
         <v>0.47583873318593983</v>
       </c>
     </row>
-    <row r="325" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B325">
         <v>266000</v>
       </c>
@@ -41351,7 +41355,7 @@
         <v>0.47494345725989845</v>
       </c>
     </row>
-    <row r="326" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B326">
         <v>267000</v>
       </c>
@@ -41392,7 +41396,7 @@
         <v>0.47405321569509623</v>
       </c>
     </row>
-    <row r="327" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B327">
         <v>268000</v>
       </c>
@@ -41433,7 +41437,7 @@
         <v>0.47316796148526313</v>
       </c>
     </row>
-    <row r="328" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B328">
         <v>269000</v>
       </c>
@@ -41474,7 +41478,7 @@
         <v>0.4722876482363052</v>
       </c>
     </row>
-    <row r="329" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B329">
         <v>270000</v>
       </c>
@@ -41515,7 +41519,7 @@
         <v>0.47141223015609252</v>
       </c>
     </row>
-    <row r="330" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B330">
         <v>271000</v>
       </c>
@@ -41556,7 +41560,7 @@
         <v>0.47054166204445402</v>
       </c>
     </row>
-    <row r="331" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B331">
         <v>272000</v>
       </c>
@@ -41597,7 +41601,7 @@
         <v>0.46967589928337505</v>
       </c>
     </row>
-    <row r="332" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B332">
         <v>273000</v>
       </c>
@@ -41638,7 +41642,7 @@
         <v>0.46881489782739244</v>
       </c>
     </row>
-    <row r="333" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B333">
         <v>274000</v>
       </c>
@@ -41679,7 +41683,7 @@
         <v>0.46795861419418294</v>
       </c>
     </row>
-    <row r="334" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B334">
         <v>275000</v>
       </c>
@@ -41720,7 +41724,7 @@
         <v>0.46710700545533951</v>
       </c>
     </row>
-    <row r="335" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B335">
         <v>276000</v>
       </c>
@@ -41761,7 +41765,7 @@
         <v>0.46626002922733201</v>
       </c>
     </row>
-    <row r="336" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B336">
         <v>277000</v>
       </c>
@@ -41802,7 +41806,7 @@
         <v>0.46541764366264732</v>
       </c>
     </row>
-    <row r="337" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B337">
         <v>278000</v>
       </c>
@@ -41843,7 +41847,7 @@
         <v>0.46457980744110516</v>
       </c>
     </row>
-    <row r="338" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B338">
         <v>279000</v>
       </c>
@@ -41884,7 +41888,7 @@
         <v>0.46374647976134487</v>
       </c>
     </row>
-    <row r="339" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B339">
         <v>280000</v>
       </c>
@@ -41925,7 +41929,7 @@
         <v>0.46291762033247957</v>
       </c>
     </row>
-    <row r="340" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B340">
         <v>281000</v>
       </c>
@@ -41966,7 +41970,7 @@
         <v>0.46209318936591454</v>
       </c>
     </row>
-    <row r="341" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B341">
         <v>282000</v>
       </c>
@@ -42007,7 +42011,7 @@
         <v>0.4612731475673244</v>
       </c>
     </row>
-    <row r="342" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B342">
         <v>283000</v>
       </c>
@@ -42048,7 +42052,7 @@
         <v>0.4604574561287868</v>
       </c>
     </row>
-    <row r="343" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B343">
         <v>284000</v>
       </c>
@@ -42089,7 +42093,7 @@
         <v>0.45964607672106855</v>
       </c>
     </row>
-    <row r="344" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B344">
         <v>285000</v>
       </c>
@@ -42130,7 +42134,7 @@
         <v>0.45883897148606062</v>
       </c>
     </row>
-    <row r="345" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B345">
         <v>286000</v>
       </c>
@@ -42171,7 +42175,7 @@
         <v>0.45803610302935915</v>
       </c>
     </row>
-    <row r="346" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B346">
         <v>287000</v>
       </c>
@@ -42212,7 +42216,7 @@
         <v>0.45723743441298792</v>
       </c>
     </row>
-    <row r="347" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B347">
         <v>288000</v>
       </c>
@@ -42253,7 +42257,7 @@
         <v>0.45644292914826107</v>
       </c>
     </row>
-    <row r="348" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B348">
         <v>289000</v>
       </c>
@@ -42294,7 +42298,7 @@
         <v>0.45565255118878062</v>
       </c>
     </row>
-    <row r="349" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B349">
         <v>290000</v>
       </c>
@@ -42335,7 +42339,7 @@
         <v>0.45486626492356763</v>
       </c>
     </row>
-    <row r="350" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B350">
         <v>291000</v>
       </c>
@@ -42376,7 +42380,7 @@
         <v>0.45408403517032347</v>
       </c>
     </row>
-    <row r="351" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B351">
         <v>292000</v>
       </c>
@@ -42417,7 +42421,7 @@
         <v>0.45330582716881707</v>
       </c>
     </row>
-    <row r="352" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B352">
         <v>293000</v>
       </c>
@@ -42458,7 +42462,7 @@
         <v>0.45253160657439773</v>
       </c>
     </row>
-    <row r="353" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B353">
         <v>294000</v>
       </c>
@@ -42499,7 +42503,7 @@
         <v>0.45176133945162822</v>
       </c>
     </row>
-    <row r="354" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B354">
         <v>295000</v>
       </c>
@@ -42540,7 +42544,7 @@
         <v>0.4509949922680378</v>
       </c>
     </row>
-    <row r="355" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="355" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B355">
         <v>296000</v>
       </c>
@@ -42581,7 +42585,7 @@
         <v>0.45023253188799039</v>
       </c>
     </row>
-    <row r="356" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B356">
         <v>297000</v>
       </c>
@@ -42622,7 +42626,7 @@
         <v>0.44947392556666704</v>
       </c>
     </row>
-    <row r="357" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B357">
         <v>298000</v>
       </c>
@@ -42663,7 +42667,7 @@
         <v>0.44871914094415943</v>
       </c>
     </row>
-    <row r="358" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B358">
         <v>299000</v>
       </c>
@@ -42704,7 +42708,7 @@
         <v>0.44796814603967183</v>
       </c>
     </row>
-    <row r="359" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B359">
         <v>300000</v>
       </c>
@@ -42745,7 +42749,7 @@
         <v>0.44722090924582969</v>
       </c>
     </row>
-    <row r="360" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B360">
         <v>301000</v>
       </c>
@@ -42786,7 +42790,7 @@
         <v>0.44647739932309266</v>
       </c>
     </row>
-    <row r="361" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B361">
         <v>302000</v>
       </c>
@@ -42827,7 +42831,7 @@
         <v>0.44573758539426828</v>
       </c>
     </row>
-    <row r="362" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B362">
         <v>303000</v>
       </c>
@@ -42868,7 +42872,7 @@
         <v>0.44500143693912697</v>
       </c>
     </row>
-    <row r="363" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B363">
         <v>304000</v>
       </c>
@@ -42909,7 +42913,7 @@
         <v>0.44426892378911315</v>
       </c>
     </row>
-    <row r="364" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B364">
         <v>305000</v>
       </c>
@@ -42950,7 +42954,7 @@
         <v>0.44354001612215255</v>
       </c>
     </row>
-    <row r="365" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B365">
         <v>306000</v>
       </c>
@@ -42991,7 +42995,7 @@
         <v>0.44281468445755251</v>
       </c>
     </row>
-    <row r="366" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B366">
         <v>307000</v>
       </c>
@@ -43032,7 +43036,7 @@
         <v>0.4420928996509943</v>
       </c>
     </row>
-    <row r="367" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B367">
         <v>308000</v>
       </c>
@@ -43073,7 +43077,7 @@
         <v>0.44137463288961404</v>
       </c>
     </row>
-    <row r="368" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B368">
         <v>309000</v>
       </c>
@@ -43114,7 +43118,7 @@
         <v>0.44065985568717225</v>
       </c>
     </row>
-    <row r="369" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="369" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B369">
         <v>310000</v>
       </c>
@@ -43155,7 +43159,7 @@
         <v>0.43994853987930849</v>
       </c>
     </row>
-    <row r="370" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="370" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B370">
         <v>311000</v>
       </c>
@@ -43196,7 +43200,7 @@
         <v>0.43924065761888009</v>
       </c>
     </row>
-    <row r="371" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B371">
         <v>312000</v>
       </c>
@@ -43237,7 +43241,7 @@
         <v>0.43853618137138339</v>
       </c>
     </row>
-    <row r="372" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B372">
         <v>313000</v>
       </c>
@@ -43278,7 +43282,7 @@
         <v>0.43783508391045523</v>
       </c>
     </row>
-    <row r="373" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="373" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B373">
         <v>314000</v>
       </c>
@@ -43319,7 +43323,7 @@
         <v>0.43713733831345347</v>
       </c>
     </row>
-    <row r="374" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="374" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B374">
         <v>315000</v>
       </c>
@@ -43360,7 +43364,7 @@
         <v>0.43644291795711454</v>
       </c>
     </row>
-    <row r="375" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="375" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B375">
         <v>316000</v>
       </c>
@@ -43401,7 +43405,7 @@
         <v>0.43575179651328688</v>
       </c>
     </row>
-    <row r="376" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="376" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B376">
         <v>317000</v>
       </c>
@@ -43442,7 +43446,7 @@
         <v>0.43506394794473818</v>
       </c>
     </row>
-    <row r="377" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="377" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B377">
         <v>318000</v>
       </c>
@@ -43483,7 +43487,7 @@
         <v>0.43437934650103549</v>
       </c>
     </row>
-    <row r="378" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="378" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B378">
         <v>319000</v>
       </c>
@@ -43524,7 +43528,7 @@
         <v>0.4336979667144964</v>
       </c>
     </row>
-    <row r="379" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="379" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B379">
         <v>320000</v>
       </c>
@@ -43565,7 +43569,7 @@
         <v>0.43301978339620928</v>
       </c>
     </row>
-    <row r="380" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="380" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B380">
         <v>321000</v>
       </c>
@@ -43606,7 +43610,7 @@
         <v>0.43234477163212276</v>
       </c>
     </row>
-    <row r="381" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="381" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B381">
         <v>322000</v>
       </c>
@@ -43647,7 +43651,7 @@
         <v>0.43167290677920123</v>
       </c>
     </row>
-    <row r="382" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B382">
         <v>323000</v>
       </c>
@@ -43688,7 +43692,7 @@
         <v>0.43100416446164613</v>
       </c>
     </row>
-    <row r="383" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="383" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B383">
         <v>324000</v>
       </c>
@@ -43729,7 +43733,7 @@
         <v>0.43033852056718164</v>
       </c>
     </row>
-    <row r="384" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B384">
         <v>325000</v>
       </c>
@@ -43770,7 +43774,7 @@
         <v>0.4296759512434028</v>
       </c>
     </row>
-    <row r="385" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B385">
         <v>326000</v>
       </c>
@@ -43811,7 +43815,7 @@
         <v>0.42901643289418595</v>
       </c>
     </row>
-    <row r="386" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B386">
         <v>327000</v>
       </c>
@@ -43852,7 +43856,7 @@
         <v>0.42835994217615875</v>
       </c>
     </row>
-    <row r="387" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B387">
         <v>328000</v>
       </c>
@@ -43893,7 +43897,7 @@
         <v>0.42770645599523044</v>
       </c>
     </row>
-    <row r="388" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B388">
         <v>329000</v>
       </c>
@@ -43934,7 +43938,7 @@
         <v>0.42705595150317921</v>
       </c>
     </row>
-    <row r="389" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B389">
         <v>330000</v>
       </c>
@@ -43975,7 +43979,7 @@
         <v>0.42640840609429687</v>
       </c>
     </row>
-    <row r="390" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B390">
         <v>331000</v>
       </c>
@@ -44016,7 +44020,7 @@
         <v>0.42576379740208981</v>
       </c>
     </row>
-    <row r="391" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B391">
         <v>332000</v>
       </c>
@@ -44057,7 +44061,7 @@
         <v>0.42512210329603345</v>
       </c>
     </row>
-    <row r="392" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B392">
         <v>333000</v>
       </c>
@@ -44098,7 +44102,7 @@
         <v>0.42448330187838201</v>
       </c>
     </row>
-    <row r="393" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B393">
         <v>334000</v>
       </c>
@@ -44139,7 +44143,7 @@
         <v>0.4238473714810288</v>
       </c>
     </row>
-    <row r="394" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B394">
         <v>335000</v>
       </c>
@@ -44180,7 +44184,7 @@
         <v>0.42321429066242022</v>
       </c>
     </row>
-    <row r="395" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B395">
         <v>336000</v>
       </c>
@@ -44221,7 +44225,7 @@
         <v>0.42258403820451867</v>
       </c>
     </row>
-    <row r="396" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B396">
         <v>337000</v>
       </c>
@@ -44262,7 +44266,7 @@
         <v>0.42195659310981593</v>
       </c>
     </row>
-    <row r="397" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B397">
         <v>338000</v>
       </c>
@@ -44303,7 +44307,7 @@
         <v>0.4213319345983948</v>
       </c>
     </row>
-    <row r="398" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B398">
         <v>339000</v>
       </c>
@@ -44344,7 +44348,7 @@
         <v>0.42071004210503887</v>
       </c>
     </row>
-    <row r="399" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B399">
         <v>340000</v>
       </c>
@@ -44385,7 +44389,7 @@
         <v>0.42009089527638854</v>
       </c>
     </row>
-    <row r="400" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B400">
         <v>341000</v>
       </c>
@@ -44426,7 +44430,7 @@
         <v>0.41947447396814325</v>
       </c>
     </row>
-    <row r="401" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B401">
         <v>342000</v>
       </c>
@@ -44467,7 +44471,7 @@
         <v>0.41886075824230851</v>
       </c>
     </row>
-    <row r="402" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B402">
         <v>343000</v>
       </c>
@@ -44508,7 +44512,7 @@
         <v>0.41824972836448793</v>
       </c>
     </row>
-    <row r="403" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B403">
         <v>344000</v>
       </c>
@@ -44549,7 +44553,7 @@
         <v>0.41764136480121705</v>
       </c>
     </row>
-    <row r="404" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B404">
         <v>345000</v>
       </c>
@@ -44590,7 +44594,7 @@
         <v>0.41703564821734124</v>
       </c>
     </row>
-    <row r="405" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B405">
         <v>346000</v>
       </c>
@@ -44631,7 +44635,7 @@
         <v>0.41643255947343433</v>
       </c>
     </row>
-    <row r="406" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B406">
         <v>347000</v>
       </c>
@@ -44672,7 +44676,7 @@
         <v>0.41583207962325858</v>
       </c>
     </row>
-    <row r="407" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B407">
         <v>348000</v>
       </c>
@@ -44713,7 +44717,7 @@
         <v>0.41523418991126482</v>
       </c>
     </row>
-    <row r="408" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B408">
         <v>349000</v>
       </c>
@@ -44754,7 +44758,7 @@
         <v>0.41463887177013209</v>
       </c>
     </row>
-    <row r="409" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B409">
         <v>350000</v>
       </c>
@@ -44795,7 +44799,7 @@
         <v>0.41404610681834525</v>
       </c>
     </row>
-    <row r="410" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B410">
         <v>351000</v>
       </c>
@@ -44836,7 +44840,7 @@
         <v>0.41345587685781188</v>
       </c>
     </row>
-    <row r="411" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B411">
         <v>352000</v>
       </c>
@@ -44877,7 +44881,7 @@
         <v>0.4128681638715152</v>
       </c>
     </row>
-    <row r="412" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B412">
         <v>353000</v>
       </c>
@@ -44918,7 +44922,7 @@
         <v>0.41228295002120446</v>
       </c>
     </row>
-    <row r="413" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B413">
         <v>354000</v>
       </c>
@@ -44959,7 +44963,7 @@
         <v>0.41170021764512044</v>
       </c>
     </row>
-    <row r="414" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B414">
         <v>355000</v>
       </c>
@@ -45000,7 +45004,7 @@
         <v>0.41111994925575712</v>
       </c>
     </row>
-    <row r="415" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B415">
         <v>356000</v>
       </c>
@@ -45041,7 +45045,7 @@
         <v>0.41054212753765729</v>
       </c>
     </row>
-    <row r="416" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B416">
         <v>357000</v>
       </c>
@@ -45082,7 +45086,7 @@
         <v>0.40996673534524219</v>
       </c>
     </row>
-    <row r="417" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B417">
         <v>358000</v>
       </c>
@@ -45123,7 +45127,7 @@
         <v>0.40939375570067493</v>
       </c>
     </row>
-    <row r="418" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B418">
         <v>359000</v>
       </c>
@@ -45164,7 +45168,7 @@
         <v>0.40882317179175631</v>
       </c>
     </row>
-    <row r="419" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B419">
         <v>360000</v>
       </c>
@@ -45205,7 +45209,7 @@
         <v>0.40825496696985275</v>
       </c>
     </row>
-    <row r="420" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B420">
         <v>361000</v>
       </c>
@@ -45246,7 +45250,7 @@
         <v>0.40768912474785629</v>
       </c>
     </row>
-    <row r="421" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B421">
         <v>362000</v>
       </c>
@@ -45287,7 +45291,7 @@
         <v>0.40712562879817499</v>
       </c>
     </row>
-    <row r="422" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B422">
         <v>363000</v>
       </c>
@@ -45328,7 +45332,7 @@
         <v>0.40656446295075427</v>
       </c>
     </row>
-    <row r="423" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B423">
         <v>364000</v>
       </c>
@@ -45369,7 +45373,7 @@
         <v>0.40600561119112794</v>
       </c>
     </row>
-    <row r="424" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B424">
         <v>365000</v>
       </c>
@@ -45410,7 +45414,7 @@
         <v>0.40544905765849842</v>
       </c>
     </row>
-    <row r="425" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B425">
         <v>366000</v>
       </c>
@@ -45451,7 +45455,7 @@
         <v>0.40489478664384665</v>
       </c>
     </row>
-    <row r="426" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B426">
         <v>367000</v>
       </c>
@@ -45492,7 +45496,7 @@
         <v>0.40434278258806927</v>
       </c>
     </row>
-    <row r="427" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B427">
         <v>368000</v>
       </c>
@@ -45533,7 +45537,7 @@
         <v>0.40379303008014433</v>
       </c>
     </row>
-    <row r="428" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B428">
         <v>369000</v>
       </c>
@@ -45574,7 +45578,7 @@
         <v>0.4032455138553242</v>
       </c>
     </row>
-    <row r="429" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B429">
         <v>370000</v>
       </c>
@@ -45615,7 +45619,7 @@
         <v>0.40270021879335532</v>
       </c>
     </row>
-    <row r="430" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B430">
         <v>371000</v>
       </c>
@@ -45656,7 +45660,7 @@
         <v>0.40215712991672437</v>
       </c>
     </row>
-    <row r="431" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B431">
         <v>372000</v>
       </c>
@@ -45697,7 +45701,7 @@
         <v>0.40161623238893063</v>
       </c>
     </row>
-    <row r="432" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B432">
         <v>373000</v>
       </c>
@@ -45738,7 +45742,7 @@
         <v>0.40107751151278337</v>
       </c>
     </row>
-    <row r="433" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B433">
         <v>374000</v>
       </c>
@@ -45779,7 +45783,7 @@
         <v>0.40054095272872436</v>
       </c>
     </row>
-    <row r="434" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B434">
         <v>375000</v>
       </c>
@@ -45820,7 +45824,7 @@
         <v>0.40000654161317578</v>
       </c>
     </row>
-    <row r="435" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B435">
         <v>376000</v>
       </c>
@@ -45861,7 +45865,7 @@
         <v>0.3994742638769111</v>
       </c>
     </row>
-    <row r="436" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B436">
         <v>377000</v>
       </c>
@@ -45902,7 +45906,7 @@
         <v>0.39894410536345065</v>
       </c>
     </row>
-    <row r="437" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B437">
         <v>378000</v>
       </c>
@@ -45943,7 +45947,7 @@
         <v>0.39841605204748032</v>
       </c>
     </row>
-    <row r="438" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B438">
         <v>379000</v>
       </c>
@@ -45984,7 +45988,7 @@
         <v>0.39789009003329284</v>
       </c>
     </row>
-    <row r="439" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B439">
         <v>380000</v>
       </c>
@@ -46025,7 +46029,7 @@
         <v>0.39736620555325219</v>
       </c>
     </row>
-    <row r="440" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B440">
         <v>381000</v>
       </c>
@@ -46066,7 +46070,7 @@
         <v>0.39684438496628005</v>
       </c>
     </row>
-    <row r="441" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B441">
         <v>382000</v>
       </c>
@@ -46107,7 +46111,7 @@
         <v>0.39632461475636371</v>
       </c>
     </row>
-    <row r="442" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B442">
         <v>383000</v>
       </c>
@@ -46148,7 +46152,7 @@
         <v>0.39580688153108573</v>
       </c>
     </row>
-    <row r="443" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="443" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B443">
         <v>384000</v>
       </c>
@@ -46189,7 +46193,7 @@
         <v>0.39529117202017472</v>
       </c>
     </row>
-    <row r="444" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="444" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B444">
         <v>385000</v>
       </c>
@@ -46230,7 +46234,7 @@
         <v>0.39477747307407657</v>
       </c>
     </row>
-    <row r="445" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B445">
         <v>386000</v>
       </c>
@@ -46271,7 +46275,7 @@
         <v>0.39426577166254645</v>
       </c>
     </row>
-    <row r="446" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="446" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B446">
         <v>387000</v>
       </c>
@@ -46312,7 +46316,7 @@
         <v>0.39375605487326032</v>
       </c>
     </row>
-    <row r="447" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="447" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B447">
         <v>388000</v>
       </c>
@@ -46353,7 +46357,7 @@
         <v>0.39324830991044663</v>
       </c>
     </row>
-    <row r="448" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="448" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B448">
         <v>389000</v>
       </c>
@@ -46394,7 +46398,7 @@
         <v>0.39274252409353699</v>
       </c>
     </row>
-    <row r="449" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="449" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B449">
         <v>390000</v>
       </c>
@@ -46435,7 +46439,7 @@
         <v>0.39223868485583607</v>
       </c>
     </row>
-    <row r="450" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="450" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B450">
         <v>391000</v>
       </c>
@@ -46476,7 +46480,7 @@
         <v>0.39173677974321042</v>
       </c>
     </row>
-    <row r="451" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="451" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B451">
         <v>392000</v>
       </c>
@@ -46517,7 +46521,7 @@
         <v>0.39123679641279518</v>
       </c>
     </row>
-    <row r="452" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="452" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B452">
         <v>393000</v>
       </c>
@@ -46558,7 +46562,7 @@
         <v>0.39073872263171933</v>
       </c>
     </row>
-    <row r="453" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="453" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B453">
         <v>394000</v>
       </c>
@@ -46599,7 +46603,7 @@
         <v>0.39024254627584859</v>
       </c>
     </row>
-    <row r="454" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="454" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B454">
         <v>395000</v>
       </c>
@@ -46640,7 +46644,7 @@
         <v>0.38974825532854612</v>
       </c>
     </row>
-    <row r="455" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="455" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B455">
         <v>396000</v>
       </c>
@@ -46681,7 +46685,7 @@
         <v>0.38925583787944951</v>
       </c>
     </row>
-    <row r="456" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="456" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B456">
         <v>397000</v>
       </c>
@@ -46722,7 +46726,7 @@
         <v>0.38876528212326633</v>
       </c>
     </row>
-    <row r="457" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="457" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B457">
         <v>398000</v>
       </c>
@@ -46763,7 +46767,7 @@
         <v>0.38827657635858454</v>
       </c>
     </row>
-    <row r="458" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="458" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B458">
         <v>399000</v>
       </c>
@@ -46804,7 +46808,7 @@
         <v>0.38778970898670062</v>
       </c>
     </row>
-    <row r="459" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="459" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B459">
         <v>400000</v>
       </c>
@@ -46845,7 +46849,7 @@
         <v>0.38730466851046352</v>
       </c>
     </row>
-    <row r="460" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="460" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B460">
         <v>401000</v>
       </c>
@@ -46886,7 +46890,7 @@
         <v>0.38682144353313375</v>
       </c>
     </row>
-    <row r="461" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="461" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B461">
         <v>402000</v>
       </c>
@@ -46927,7 +46931,7 @@
         <v>0.38634002275725926</v>
       </c>
     </row>
-    <row r="462" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="462" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B462">
         <v>403000</v>
       </c>
@@ -46968,7 +46972,7 @@
         <v>0.38586039498356584</v>
       </c>
     </row>
-    <row r="463" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="463" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B463">
         <v>404000</v>
       </c>
@@ -47009,7 +47013,7 @@
         <v>0.38538254910986286</v>
       </c>
     </row>
-    <row r="464" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="464" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B464">
         <v>405000</v>
       </c>
@@ -47050,7 +47054,7 @@
         <v>0.38490647412996382</v>
       </c>
     </row>
-    <row r="465" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="465" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B465">
         <v>406000</v>
       </c>
@@ -47091,7 +47095,7 @@
         <v>0.3844321591326218</v>
       </c>
     </row>
-    <row r="466" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="466" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B466">
         <v>407000</v>
       </c>
@@ -47132,7 +47136,7 @@
         <v>0.38395959330047907</v>
       </c>
     </row>
-    <row r="467" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B467">
         <v>408000</v>
       </c>
@@ -47173,7 +47177,7 @@
         <v>0.38348876590903075</v>
       </c>
     </row>
-    <row r="468" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="468" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B468">
         <v>409000</v>
       </c>
@@ -47214,7 +47218,7 @@
         <v>0.38301966632560269</v>
       </c>
     </row>
-    <row r="469" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="469" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B469">
         <v>410000</v>
       </c>
@@ -47255,7 +47259,7 @@
         <v>0.38255228400834312</v>
       </c>
     </row>
-    <row r="470" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="470" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B470">
         <v>411000</v>
       </c>
@@ -47296,7 +47300,7 @@
         <v>0.38208660850522724</v>
       </c>
     </row>
-    <row r="471" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="471" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B471">
         <v>412000</v>
       </c>
@@ -47337,7 +47341,7 @@
         <v>0.38162262945307585</v>
       </c>
     </row>
-    <row r="472" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="472" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B472">
         <v>413000</v>
       </c>
@@ -47378,7 +47382,7 @@
         <v>0.3811603365765866</v>
       </c>
     </row>
-    <row r="473" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="473" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B473">
         <v>414000</v>
       </c>
@@ -47419,7 +47423,7 @@
         <v>0.38069971968737815</v>
       </c>
     </row>
-    <row r="474" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="474" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B474">
         <v>415000</v>
       </c>
@@ -47460,7 +47464,7 @@
         <v>0.38024076868304729</v>
       </c>
     </row>
-    <row r="475" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="475" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B475">
         <v>416000</v>
       </c>
@@ -47501,7 +47505,7 @@
         <v>0.37978347354623815</v>
       </c>
     </row>
-    <row r="476" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="476" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B476">
         <v>417000</v>
       </c>
@@ -47542,7 +47546,7 @@
         <v>0.37932782434372375</v>
       </c>
     </row>
-    <row r="477" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="477" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B477">
         <v>418000</v>
       </c>
@@ -47583,7 +47587,7 @@
         <v>0.37887381122550012</v>
       </c>
     </row>
-    <row r="478" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="478" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B478">
         <v>419000</v>
       </c>
@@ -47624,7 +47628,7 @@
         <v>0.37842142442389165</v>
       </c>
     </row>
-    <row r="479" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="479" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B479">
         <v>420000</v>
       </c>
@@ -47665,7 +47669,7 @@
         <v>0.37797065425266879</v>
       </c>
     </row>
-    <row r="480" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="480" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B480">
         <v>421000</v>
       </c>
@@ -47706,7 +47710,7 @@
         <v>0.3775214911061765</v>
       </c>
     </row>
-    <row r="481" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="481" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B481">
         <v>422000</v>
       </c>
@@ -47747,7 +47751,7 @@
         <v>0.37707392545847496</v>
       </c>
     </row>
-    <row r="482" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="482" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B482">
         <v>423000</v>
       </c>
@@ -47788,7 +47792,7 @@
         <v>0.37662794786249082</v>
       </c>
     </row>
-    <row r="483" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="483" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B483">
         <v>424000</v>
       </c>
@@ -47829,7 +47833,7 @@
         <v>0.37618354894917982</v>
       </c>
     </row>
-    <row r="484" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="484" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B484">
         <v>425000</v>
       </c>
@@ -47870,7 +47874,7 @@
         <v>0.37574071942670001</v>
       </c>
     </row>
-    <row r="485" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="485" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B485">
         <v>426000</v>
       </c>
@@ -47911,7 +47915,7 @@
         <v>0.3752994500795957</v>
       </c>
     </row>
-    <row r="486" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="486" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B486">
         <v>427000</v>
       </c>
@@ -47952,7 +47956,7 @@
         <v>0.37485973176799203</v>
       </c>
     </row>
-    <row r="487" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="487" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B487">
         <v>428000</v>
       </c>
@@ -47993,7 +47997,7 @@
         <v>0.3744215554268</v>
       </c>
     </row>
-    <row r="488" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="488" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B488">
         <v>429000</v>
       </c>
@@ -48034,7 +48038,7 @@
         <v>0.3739849120649314</v>
       </c>
     </row>
-    <row r="489" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="489" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B489">
         <v>430000</v>
       </c>
@@ -48075,7 +48079,7 @@
         <v>0.37354979276452371</v>
       </c>
     </row>
-    <row r="490" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="490" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B490">
         <v>431000</v>
       </c>
@@ -48116,7 +48120,7 @@
         <v>0.37311618868017565</v>
       </c>
     </row>
-    <row r="491" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="491" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B491">
         <v>432000</v>
       </c>
@@ -48157,7 +48161,7 @@
         <v>0.37268409103819139</v>
       </c>
     </row>
-    <row r="492" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="492" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B492">
         <v>433000</v>
       </c>
@@ -48198,7 +48202,7 @@
         <v>0.3722534911358355</v>
       </c>
     </row>
-    <row r="493" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="493" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B493">
         <v>434000</v>
       </c>
@@ -48239,7 +48243,7 @@
         <v>0.37182438034059601</v>
       </c>
     </row>
-    <row r="494" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="494" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B494">
         <v>435000</v>
       </c>
@@ -48280,7 +48284,7 @@
         <v>0.37139675008945822</v>
       </c>
     </row>
-    <row r="495" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="495" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B495">
         <v>436000</v>
       </c>
@@ -48321,7 +48325,7 @@
         <v>0.37097059188818665</v>
       </c>
     </row>
-    <row r="496" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="496" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B496">
         <v>437000</v>
       </c>
@@ -48362,7 +48366,7 @@
         <v>0.37054589731061655</v>
       </c>
     </row>
-    <row r="497" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="497" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B497">
         <v>438000</v>
       </c>
@@ -48403,7 +48407,7 @@
         <v>0.37012265799795385</v>
       </c>
     </row>
-    <row r="498" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="498" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B498">
         <v>439000</v>
       </c>
@@ -48444,7 +48448,7 @@
         <v>0.36970086565808463</v>
       </c>
     </row>
-    <row r="499" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="499" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B499">
         <v>440000</v>
       </c>
@@ -48485,7 +48489,7 @@
         <v>0.36928051206489232</v>
       </c>
     </row>
-    <row r="500" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="500" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B500">
         <v>441000</v>
       </c>
@@ -48526,7 +48530,7 @@
         <v>0.36886158905758426</v>
       </c>
     </row>
-    <row r="501" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="501" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B501">
         <v>442000</v>
       </c>
@@ -48567,7 +48571,7 @@
         <v>0.36844408854002597</v>
       </c>
     </row>
-    <row r="502" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="502" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B502">
         <v>443000</v>
       </c>
@@ -48608,7 +48612,7 @@
         <v>0.3680280024800841</v>
       </c>
     </row>
-    <row r="503" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="503" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B503">
         <v>444000</v>
       </c>
@@ -48649,7 +48653,7 @@
         <v>0.36761332290897752</v>
       </c>
     </row>
-    <row r="504" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="504" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B504">
         <v>445000</v>
       </c>
@@ -48690,7 +48694,7 @@
         <v>0.36720004192063599</v>
       </c>
     </row>
-    <row r="505" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="505" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B505">
         <v>446000</v>
       </c>
@@ -48731,7 +48735,7 @@
         <v>0.36678815167106749</v>
       </c>
     </row>
-    <row r="506" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="506" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B506">
         <v>447000</v>
       </c>
@@ -48772,7 +48776,7 @@
         <v>0.36637764437773257</v>
       </c>
     </row>
-    <row r="507" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="507" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B507">
         <v>448000</v>
       </c>
@@ -48813,7 +48817,7 @@
         <v>0.36596851231892691</v>
       </c>
     </row>
-    <row r="508" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="508" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B508">
         <v>449000</v>
       </c>
@@ -48854,7 +48858,7 @@
         <v>0.36556074783317133</v>
       </c>
     </row>
-    <row r="509" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="509" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B509">
         <v>450000</v>
       </c>
@@ -48895,7 +48899,7 @@
         <v>0.3651543433186088</v>
       </c>
     </row>
-    <row r="510" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="510" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B510">
         <v>451000</v>
       </c>
@@ -48936,7 +48940,7 @@
         <v>0.36474929123240996</v>
       </c>
     </row>
-    <row r="511" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="511" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B511">
         <v>452000</v>
       </c>
@@ -48977,7 +48981,7 @@
         <v>0.36434558409018453</v>
       </c>
     </row>
-    <row r="512" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="512" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B512">
         <v>453000</v>
       </c>
@@ -49018,7 +49022,7 @@
         <v>0.36394321446540034</v>
       </c>
     </row>
-    <row r="513" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="513" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B513">
         <v>454000</v>
       </c>
@@ -49059,7 +49063,7 @@
         <v>0.3635421749888102</v>
       </c>
     </row>
-    <row r="514" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="514" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B514">
         <v>455000</v>
       </c>
@@ -49100,7 +49104,7 @@
         <v>0.36314245834788456</v>
       </c>
     </row>
-    <row r="515" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="515" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B515">
         <v>456000</v>
       </c>
@@ -49141,7 +49145,7 @@
         <v>0.36274405728625142</v>
       </c>
     </row>
-    <row r="516" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="516" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B516">
         <v>457000</v>
       </c>
@@ -49182,7 +49186,7 @@
         <v>0.36234696460314331</v>
       </c>
     </row>
-    <row r="517" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="517" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B517">
         <v>458000</v>
       </c>
@@ -49223,7 +49227,7 @@
         <v>0.36195117315285069</v>
       </c>
     </row>
-    <row r="518" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="518" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B518">
         <v>459000</v>
       </c>
@@ -49264,7 +49268,7 @@
         <v>0.36155667584418155</v>
       </c>
     </row>
-    <row r="519" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="519" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B519">
         <v>460000</v>
       </c>
@@ -49305,7 +49309,7 @@
         <v>0.36116346563992802</v>
       </c>
     </row>
-    <row r="520" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="520" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B520">
         <v>461000</v>
       </c>
@@ -49346,7 +49350,7 @@
         <v>0.36077153555633923</v>
       </c>
     </row>
-    <row r="521" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="521" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B521">
         <v>462000</v>
       </c>
@@ -49387,7 +49391,7 @@
         <v>0.3603808786626001</v>
       </c>
     </row>
-    <row r="522" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="522" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B522">
         <v>463000</v>
       </c>
@@ -49428,7 +49432,7 @@
         <v>0.35999148808031667</v>
       </c>
     </row>
-    <row r="523" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="523" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B523">
         <v>464000</v>
       </c>
@@ -49469,7 +49473,7 @@
         <v>0.35960335698300744</v>
       </c>
     </row>
-    <row r="524" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="524" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B524">
         <v>465000</v>
       </c>
@@ -49510,7 +49514,7 @@
         <v>0.35921647859560074</v>
       </c>
     </row>
-    <row r="525" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="525" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B525">
         <v>466000</v>
       </c>
@@ -49551,7 +49555,7 @@
         <v>0.35883084619393785</v>
       </c>
     </row>
-    <row r="526" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="526" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B526">
         <v>467000</v>
       </c>
@@ -49592,7 +49596,7 @@
         <v>0.35844645310428264</v>
       </c>
     </row>
-    <row r="527" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="527" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B527">
         <v>468000</v>
       </c>
@@ -49651,22 +49655,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42776B4E-36EB-4BD7-9F21-29E0904C8457}">
   <dimension ref="C2:N519"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="20.44140625" customWidth="1"/>
-    <col min="12" max="12" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D3" s="73" t="s">
         <v>92</v>
       </c>
@@ -49681,7 +49685,7 @@
       <c r="M3" s="73"/>
       <c r="N3" s="73"/>
     </row>
-    <row r="4" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D4" s="46" t="s">
         <v>74</v>
       </c>
@@ -49716,7 +49720,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D5" s="48" t="s">
         <v>75</v>
       </c>
@@ -49753,7 +49757,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D6" s="13" t="s">
         <v>83</v>
       </c>
@@ -49791,7 +49795,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D7" s="13" t="s">
         <v>84</v>
       </c>
@@ -49829,7 +49833,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D8" s="54" t="s">
         <v>90</v>
       </c>
@@ -49867,8 +49871,8 @@
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D13" s="74" t="s">
         <v>75</v>
       </c>
@@ -49886,7 +49890,7 @@
       </c>
       <c r="K13" s="75"/>
     </row>
-    <row r="14" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D14" s="36" t="s">
         <v>20</v>
       </c>
@@ -49912,7 +49916,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="15" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D15" s="36" t="s">
         <v>72</v>
       </c>
@@ -49942,7 +49946,7 @@
         <v>67584974973.343758</v>
       </c>
     </row>
-    <row r="16" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
         <v>94</v>
       </c>
@@ -49971,7 +49975,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C17" s="16">
         <v>0</v>
       </c>
@@ -50008,7 +50012,7 @@
         <v>13.064039525375183</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C18" s="16">
         <v>0.1</v>
       </c>
@@ -50045,7 +50049,7 @@
         <v>12.309988559128836</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C19" s="16">
         <v>0.2</v>
       </c>
@@ -50082,7 +50086,7 @@
         <v>11.673047168078822</v>
       </c>
     </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C20" s="16">
         <v>0.3</v>
       </c>
@@ -50119,7 +50123,7 @@
         <v>11.12573617544855</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C21" s="16">
         <v>0.4</v>
       </c>
@@ -50156,7 +50160,7 @@
         <v>10.648831345066812</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C22" s="16">
         <v>0.5</v>
       </c>
@@ -50193,7 +50197,7 @@
         <v>10.228426286242756</v>
       </c>
     </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C23" s="16">
         <v>0.6</v>
       </c>
@@ -50230,7 +50234,7 @@
         <v>9.854179270727311</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C24" s="16">
         <v>0.7</v>
       </c>
@@ -50267,7 +50271,7 @@
         <v>9.5182183835795513</v>
       </c>
     </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C25" s="16">
         <v>0.8</v>
       </c>
@@ -50304,7 +50308,7 @@
         <v>9.2144314775220639</v>
       </c>
     </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C26" s="16">
         <v>0.9</v>
       </c>
@@ -50341,7 +50345,7 @@
         <v>8.9379906731578078</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C27" s="16">
         <v>1</v>
       </c>
@@ -50378,7 +50382,7 @@
         <v>8.6850250182981057</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C28" s="16">
         <v>1.1000000000000001</v>
       </c>
@@ -50415,7 +50419,7 @@
         <v>8.4523896675632244</v>
       </c>
     </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C29" s="16">
         <v>1.2</v>
       </c>
@@ -50452,7 +50456,7 @@
         <v>8.2374996555779205</v>
       </c>
     </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C30" s="16">
         <v>1.3</v>
       </c>
@@ -50489,7 +50493,7 @@
         <v>8.0382079334512984</v>
       </c>
     </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C31" s="16">
         <v>1.4</v>
       </c>
@@ -50526,7 +50530,7 @@
         <v>7.8527143810825759</v>
       </c>
     </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C32" s="16">
         <v>1.5</v>
       </c>
@@ -50563,7 +50567,7 @@
         <v>7.6794969074548671</v>
       </c>
     </row>
-    <row r="33" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C33" s="16">
         <v>1.6</v>
       </c>
@@ -50600,7 +50604,7 @@
         <v>7.5172585693932898</v>
       </c>
     </row>
-    <row r="34" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C34" s="16">
         <v>1.7</v>
       </c>
@@ -50637,7 +50641,7 @@
         <v>7.3648864857585519</v>
       </c>
     </row>
-    <row r="35" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C35" s="16">
         <v>1.8</v>
       </c>
@@ -50674,7 +50678,7 @@
         <v>7.2214195586736878</v>
       </c>
     </row>
-    <row r="36" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C36" s="16">
         <v>1.9</v>
       </c>
@@ -50711,7 +50715,7 @@
         <v>7.0860228542563215</v>
       </c>
     </row>
-    <row r="37" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C37" s="16">
         <v>2</v>
       </c>
@@ -50748,7 +50752,7 @@
         <v>6.9579670777340397</v>
       </c>
     </row>
-    <row r="38" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C38" s="16">
         <v>2.1</v>
       </c>
@@ -50785,7 +50789,7 @@
         <v>6.8366119874571432</v>
       </c>
     </row>
-    <row r="39" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C39" s="16">
         <v>2.2000000000000002</v>
       </c>
@@ -50822,7 +50826,7 @@
         <v>6.7213928845429702</v>
       </c>
     </row>
-    <row r="40" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C40" s="16">
         <v>2.2999999999999998</v>
       </c>
@@ -50859,7 +50863,7 @@
         <v>6.6118095260789707</v>
       </c>
     </row>
-    <row r="41" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C41" s="16">
         <v>2.4</v>
       </c>
@@ -50896,7 +50900,7 @@
         <v>6.5074169642960387</v>
       </c>
     </row>
-    <row r="42" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C42" s="16">
         <v>2.5</v>
       </c>
@@ -50933,7 +50937,7 @@
         <v>6.4078179283972734</v>
       </c>
     </row>
-    <row r="43" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C43" s="16">
         <v>2.6</v>
       </c>
@@ -50970,7 +50974,7 @@
         <v>6.3126564511409882</v>
       </c>
     </row>
-    <row r="44" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C44" s="16">
         <v>2.7</v>
       </c>
@@ -51007,7 +51011,7 @@
         <v>6.2216125067417751</v>
       </c>
     </row>
-    <row r="45" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C45" s="16">
         <v>2.8</v>
       </c>
@@ -51044,7 +51048,7 @@
         <v>6.1343974757512418</v>
       </c>
     </row>
-    <row r="46" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C46" s="16">
         <v>2.9</v>
       </c>
@@ -51081,7 +51085,7 @@
         <v>6.0507502902932755</v>
       </c>
     </row>
-    <row r="47" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C47" s="16">
         <v>3</v>
       </c>
@@ -51118,7 +51122,7 @@
         <v>5.970434142229549</v>
       </c>
     </row>
-    <row r="48" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C48" s="16">
         <v>3.1</v>
       </c>
@@ -51155,7 +51159,7 @@
         <v>5.8932336596112327</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C49" s="16">
         <v>3.2</v>
       </c>
@@ -51192,7 +51196,7 @@
         <v>5.8189524746707484</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C50" s="16">
         <v>3.3</v>
       </c>
@@ -51229,7 +51233,7 @@
         <v>5.7474111207636005</v>
       </c>
     </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C51" s="16">
         <v>3.4</v>
       </c>
@@ -51266,7 +51270,7 @@
         <v>5.6784452069381066</v>
       </c>
     </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C52" s="16">
         <v>3.5</v>
       </c>
@@ -51303,7 +51307,7 @@
         <v>5.611903827833614</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C53" s="16">
         <v>3.6</v>
       </c>
@@ -51340,7 +51344,7 @@
         <v>5.5476481738738173</v>
       </c>
     </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C54" s="16">
         <v>3.7</v>
       </c>
@@ -51377,7 +51381,7 @@
         <v>5.4855503126050165</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C55" s="16">
         <v>3.8</v>
       </c>
@@ -51414,7 +51418,7 @@
         <v>5.4254921168170993</v>
       </c>
     </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C56" s="16">
         <v>3.9</v>
       </c>
@@ -51451,7 +51455,7 @@
         <v>5.3673643190008171</v>
       </c>
     </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C57" s="16">
         <v>4</v>
       </c>
@@ -51488,7 +51492,7 @@
         <v>5.3110656749123288</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C58" s="16">
         <v>4.0999999999999996</v>
       </c>
@@ -51525,7 +51529,7 @@
         <v>5.2565022216714157</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C59" s="16">
         <v>4.2</v>
       </c>
@@ -51562,7 +51566,7 @@
         <v>5.2035866180206414</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C60" s="16">
         <v>4.3</v>
       </c>
@@ -51599,7 +51603,7 @@
         <v>5.1522375562044056</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C61" s="16">
         <v>4.4000000000000004</v>
       </c>
@@ -51636,7 +51640,7 @@
         <v>5.1023792364571028</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C62" s="16">
         <v>4.5</v>
       </c>
@@ -51673,7 +51677,7 @@
         <v>5.0539408963728638</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C63" s="16">
         <v>4.5999999999999996</v>
       </c>
@@ -51710,7 +51714,7 @@
         <v>5.0068563885093793</v>
       </c>
     </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C64" s="16">
         <v>4.7</v>
       </c>
@@ -51747,7 +51751,7 @@
         <v>4.9610638004903711</v>
       </c>
     </row>
-    <row r="65" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C65" s="16">
         <v>4.8</v>
       </c>
@@ -51784,7 +51788,7 @@
         <v>4.9165051126440558</v>
       </c>
     </row>
-    <row r="66" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C66" s="16">
         <v>4.9000000000000004</v>
       </c>
@@ -51821,7 +51825,7 @@
         <v>4.8731258888718036</v>
       </c>
     </row>
-    <row r="67" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C67" s="16">
         <v>5</v>
       </c>
@@ -51858,7 +51862,7 @@
         <v>4.8308749970012519</v>
       </c>
     </row>
-    <row r="68" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C68" s="16">
         <v>5.0999999999999996</v>
       </c>
@@ -51895,7 +51899,7 @@
         <v>4.7897043553569816</v>
       </c>
     </row>
-    <row r="69" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C69" s="16">
         <v>5.2</v>
       </c>
@@ -51932,7 +51936,7 @@
         <v>4.7495687026925628</v>
       </c>
     </row>
-    <row r="70" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C70" s="16">
         <v>5.3</v>
       </c>
@@ -51969,7 +51973,7 @@
         <v>4.7104253889808652</v>
       </c>
     </row>
-    <row r="71" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C71" s="16">
         <v>5.4</v>
       </c>
@@ -52006,7 +52010,7 @@
         <v>4.6722341848640045</v>
       </c>
     </row>
-    <row r="72" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C72" s="16">
         <v>5.5</v>
       </c>
@@ -52043,7 +52047,7 @@
         <v>4.6349571078274066</v>
       </c>
     </row>
-    <row r="73" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C73" s="16">
         <v>5.6</v>
       </c>
@@ -52080,7 +52084,7 @@
         <v>4.5985582633905135</v>
       </c>
     </row>
-    <row r="74" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C74" s="16">
         <v>5.7</v>
       </c>
@@ -52117,7 +52121,7 @@
         <v>4.5630036998046837</v>
       </c>
     </row>
-    <row r="75" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C75" s="16">
         <v>5.8</v>
       </c>
@@ -52154,7 +52158,7 @@
         <v>4.5282612749212454</v>
       </c>
     </row>
-    <row r="76" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C76" s="16">
         <v>5.9</v>
       </c>
@@ -52191,7 +52195,7 @@
         <v>4.4943005340430879</v>
       </c>
     </row>
-    <row r="77" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C77" s="16">
         <v>6</v>
       </c>
@@ -52228,7 +52232,7 @@
         <v>4.4610925977046891</v>
       </c>
     </row>
-    <row r="78" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C78" s="16">
         <v>6.1</v>
       </c>
@@ -52265,7 +52269,7 @@
         <v>4.4286100584407411</v>
       </c>
     </row>
-    <row r="79" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C79" s="16">
         <v>6.2</v>
       </c>
@@ -52302,7 +52306,7 @@
         <v>4.3968268857047086</v>
       </c>
     </row>
-    <row r="80" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C80" s="16">
         <v>6.3</v>
       </c>
@@ -52339,7 +52343,7 @@
         <v>4.3657183381876541</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C81" s="16">
         <v>6.4</v>
       </c>
@@ -52376,7 +52380,7 @@
         <v>4.3352608828661499</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C82" s="16">
         <v>6.5</v>
       </c>
@@ -52413,7 +52417,7 @@
         <v>4.3054321201773327</v>
       </c>
     </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C83" s="16">
         <v>6.6</v>
       </c>
@@ -52450,7 +52454,7 @@
         <v>4.2762107147804818</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C84" s="16">
         <v>6.7</v>
       </c>
@@ -52487,7 +52491,7 @@
         <v>4.2475763314187756</v>
       </c>
     </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C85" s="16">
         <v>6.8</v>
       </c>
@@ -52524,7 +52528,7 @@
         <v>4.2195095754430989</v>
       </c>
     </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C86" s="16">
         <v>6.9</v>
       </c>
@@ -52561,7 +52565,7 @@
         <v>4.1919919376026442</v>
       </c>
     </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C87" s="16">
         <v>7</v>
       </c>
@@ -52598,7 +52602,7 @@
         <v>4.1650057427452074</v>
       </c>
     </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C88" s="16">
         <v>7.1</v>
       </c>
@@ -52635,7 +52639,7 @@
         <v>4.1385341021041144</v>
       </c>
     </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C89" s="16">
         <v>7.2</v>
       </c>
@@ -52672,7 +52676,7 @@
         <v>4.1125608688791679</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C90" s="16">
         <v>7.3</v>
       </c>
@@ -52709,7 +52713,7 @@
         <v>4.0870705968461678</v>
       </c>
     </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C91" s="16">
         <v>7.4</v>
       </c>
@@ -52746,7 +52750,7 @@
         <v>4.0620485017539494</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C92" s="16">
         <v>7.5</v>
       </c>
@@ -52783,7 +52787,7 @@
         <v>4.0374804252897754</v>
       </c>
     </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C93" s="16">
         <v>7.6</v>
       </c>
@@ -52820,7 +52824,7 @@
         <v>4.013352801413534</v>
       </c>
     </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C94" s="16">
         <v>7.7</v>
       </c>
@@ -52857,7 +52861,7 @@
         <v>3.9896526248788824</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C95" s="16">
         <v>7.8</v>
       </c>
@@ -52894,7 +52898,7 @@
         <v>3.9663674217754155</v>
       </c>
     </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C96" s="16">
         <v>7.9</v>
       </c>
@@ -52931,7 +52935,7 @@
         <v>3.9434852219402625</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C97" s="16">
         <v>8</v>
       </c>
@@ -52968,7 +52972,7 @@
         <v>3.9209945331005156</v>
       </c>
     </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C98" s="16">
         <v>8.1</v>
       </c>
@@ -53005,7 +53009,7 @@
         <v>3.8988843166196032</v>
       </c>
     </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C99" s="16">
         <v>8.1999999999999993</v>
       </c>
@@ -53042,7 +53046,7 @@
         <v>3.877143964731335</v>
       </c>
     </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C100" s="16">
         <v>8.3000000000000007</v>
       </c>
@@ -53079,7 +53083,7 @@
         <v>3.8557632791549641</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C101" s="16">
         <v>8.4</v>
       </c>
@@ -53116,7 +53120,7 @@
         <v>3.8347324509933451</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C102" s="16">
         <v>8.5</v>
       </c>
@@ -53153,7 +53157,7 @@
         <v>3.8140420418241798</v>
       </c>
     </row>
-    <row r="103" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C103" s="16">
         <v>8.6</v>
       </c>
@@ -53190,7 +53194,7 @@
         <v>3.7936829659015614</v>
       </c>
     </row>
-    <row r="104" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C104" s="16">
         <v>8.6999999999999993</v>
       </c>
@@ -53227,7 +53231,7 @@
         <v>3.7736464733915787</v>
       </c>
     </row>
-    <row r="105" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C105" s="16">
         <v>8.8000000000000007</v>
       </c>
@@ -53264,7 +53268,7 @@
         <v>3.7539241345717214</v>
       </c>
     </row>
-    <row r="106" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C106" s="16">
         <v>8.9</v>
       </c>
@@ -53301,7 +53305,7 @@
         <v>3.7345078249292851</v>
       </c>
     </row>
-    <row r="107" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C107" s="16">
         <v>9</v>
       </c>
@@ -53338,7 +53342,7 @@
         <v>3.7153897110989336</v>
       </c>
     </row>
-    <row r="108" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C108" s="16">
         <v>9.1</v>
       </c>
@@ -53375,7 +53379,7 @@
         <v>3.6965622375841516</v>
       </c>
     </row>
-    <row r="109" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C109" s="16">
         <v>9.1999999999999993</v>
       </c>
@@ -53412,7 +53416,7 @@
         <v>3.6780181142114468</v>
       </c>
     </row>
-    <row r="110" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C110" s="16">
         <v>9.3000000000000007</v>
       </c>
@@ -53449,7 +53453,7 @@
         <v>3.6597503042700046</v>
       </c>
     </row>
-    <row r="111" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C111" s="16">
         <v>9.4</v>
       </c>
@@ -53486,7 +53490,7 @@
         <v>3.6417520132929622</v>
       </c>
     </row>
-    <row r="112" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C112" s="16">
         <v>9.5</v>
       </c>
@@ -53523,7 +53527,7 @@
         <v>3.6240166784396797</v>
       </c>
     </row>
-    <row r="113" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C113" s="16">
         <v>9.6</v>
       </c>
@@ -53560,7 +53564,7 @@
         <v>3.6065379584413311</v>
       </c>
     </row>
-    <row r="114" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C114" s="16">
         <v>9.6999999999999993</v>
       </c>
@@ -53597,7 +53601,7 @@
         <v>3.5893097240748277</v>
       </c>
     </row>
-    <row r="115" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C115" s="16">
         <v>9.8000000000000007</v>
       </c>
@@ -53634,7 +53638,7 @@
         <v>3.5723260491325721</v>
       </c>
     </row>
-    <row r="116" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C116" s="16">
         <v>9.9</v>
       </c>
@@ -53671,7 +53675,7 @@
         <v>3.5555812018578368</v>
       </c>
     </row>
-    <row r="117" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C117" s="16">
         <v>10</v>
       </c>
@@ -53708,7 +53712,7 @@
         <v>3.5390696368176453</v>
       </c>
     </row>
-    <row r="118" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C118" s="16">
         <v>10.1</v>
       </c>
@@ -53745,7 +53749,7 @@
         <v>3.5227859871869982</v>
       </c>
     </row>
-    <row r="119" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C119" s="16">
         <v>10.199999999999999</v>
       </c>
@@ -53782,7 +53786,7 @@
         <v>3.5067250574200504</v>
       </c>
     </row>
-    <row r="120" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C120" s="16">
         <v>10.3</v>
       </c>
@@ -53819,7 +53823,7 @@
         <v>3.490881816285528</v>
       </c>
     </row>
-    <row r="121" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C121" s="16">
         <v>10.4</v>
       </c>
@@ -53856,7 +53860,7 @@
         <v>3.475251390245166</v>
       </c>
     </row>
-    <row r="122" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C122" s="16">
         <v>10.5</v>
       </c>
@@ -53893,7 +53897,7 @@
         <v>3.4598290571553911</v>
       </c>
     </row>
-    <row r="123" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C123" s="16">
         <v>10.6</v>
       </c>
@@ -53930,7 +53934,7 @@
         <v>3.4446102402737573</v>
       </c>
     </row>
-    <row r="124" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C124" s="16">
         <v>10.7</v>
       </c>
@@ -53967,7 +53971,7 @@
         <v>3.4295905025528621</v>
       </c>
     </row>
-    <row r="125" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C125" s="16">
         <v>10.8</v>
       </c>
@@ -54004,7 +54008,7 @@
         <v>3.4147655412055844</v>
       </c>
     </row>
-    <row r="126" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C126" s="16">
         <v>10.9</v>
       </c>
@@ -54041,7 +54045,7 @@
         <v>3.4001311825265335</v>
       </c>
     </row>
-    <row r="127" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C127" s="16">
         <v>11</v>
       </c>
@@ -54078,7 +54082,7 @@
         <v>3.3856833769555554</v>
       </c>
     </row>
-    <row r="128" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C128" s="16">
         <v>11.1</v>
       </c>
@@ -54115,7 +54119,7 @@
         <v>3.3714181943700274</v>
       </c>
     </row>
-    <row r="129" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C129" s="16">
         <v>11.2</v>
       </c>
@@ -54152,7 +54156,7 @@
         <v>3.3573318195935289</v>
       </c>
     </row>
-    <row r="130" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C130" s="16">
         <v>11.3</v>
       </c>
@@ -54189,7 +54193,7 @@
         <v>3.3434205481092234</v>
       </c>
     </row>
-    <row r="131" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C131" s="16">
         <v>11.4</v>
       </c>
@@ -54226,7 +54230,7 @@
         <v>3.3296807819670171</v>
       </c>
     </row>
-    <row r="132" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C132" s="16">
         <v>11.5</v>
       </c>
@@ -54263,7 +54267,7 @@
         <v>3.3161090258742254</v>
       </c>
     </row>
-    <row r="133" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C133" s="16">
         <v>11.6</v>
       </c>
@@ -54300,7 +54304,7 @@
         <v>3.3027018834601067</v>
       </c>
     </row>
-    <row r="134" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C134" s="16">
         <v>11.7</v>
       </c>
@@ -54337,7 +54341,7 @@
         <v>3.2894560537051909</v>
       </c>
     </row>
-    <row r="135" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C135" s="16">
         <v>11.8</v>
       </c>
@@ -54374,7 +54378,7 @@
         <v>3.2763683275268836</v>
       </c>
     </row>
-    <row r="136" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C136" s="16">
         <v>11.9</v>
       </c>
@@ -54411,7 +54415,7 @@
         <v>3.2634355845133283</v>
       </c>
     </row>
-    <row r="137" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C137" s="16">
         <v>12</v>
       </c>
@@ -54448,7 +54452,7 @@
         <v>3.2506547897979705</v>
       </c>
     </row>
-    <row r="138" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C138" s="16">
         <v>12.1</v>
       </c>
@@ -54485,7 +54489,7 @@
         <v>3.2380229910677247</v>
       </c>
     </row>
-    <row r="139" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C139" s="16">
         <v>12.2</v>
       </c>
@@ -54522,7 +54526,7 @@
         <v>3.225537315698046</v>
       </c>
     </row>
-    <row r="140" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C140" s="16">
         <v>12.3</v>
       </c>
@@ -54559,7 +54563,7 @@
         <v>3.2131949680085787</v>
       </c>
     </row>
-    <row r="141" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C141" s="16">
         <v>12.4</v>
       </c>
@@ -54596,7 +54600,7 @@
         <v>3.2009932266334569</v>
       </c>
     </row>
-    <row r="142" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C142" s="16">
         <v>12.5</v>
       </c>
@@ -54633,7 +54637,7 @@
         <v>3.1889294420006133</v>
       </c>
     </row>
-    <row r="143" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C143" s="16">
         <v>12.6</v>
       </c>
@@ -54670,7 +54674,7 @@
         <v>3.1770010339148116</v>
       </c>
     </row>
-    <row r="144" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C144" s="16">
         <v>12.7</v>
       </c>
@@ -54707,7 +54711,7 @@
         <v>3.1652054892393862</v>
       </c>
     </row>
-    <row r="145" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C145" s="16">
         <v>12.8</v>
       </c>
@@ -54744,7 +54748,7 @@
         <v>3.1535403596719687</v>
       </c>
     </row>
-    <row r="146" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C146" s="16">
         <v>12.9</v>
       </c>
@@ -54781,7 +54785,7 @@
         <v>3.1420032596097274</v>
       </c>
     </row>
-    <row r="147" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C147" s="16">
         <v>13</v>
       </c>
@@ -54818,7 +54822,7 @@
         <v>3.130591864099888</v>
       </c>
     </row>
-    <row r="148" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C148" s="16">
         <v>13.1</v>
       </c>
@@ -54855,7 +54859,7 @@
         <v>3.1193039068715467</v>
       </c>
     </row>
-    <row r="149" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C149" s="16">
         <v>13.2</v>
       </c>
@@ -54892,7 +54896,7 @@
         <v>3.10813717844499</v>
       </c>
     </row>
-    <row r="150" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C150" s="16">
         <v>13.3</v>
       </c>
@@ -54929,7 +54933,7 @@
         <v>3.0970895243149354</v>
       </c>
     </row>
-    <row r="151" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C151" s="16">
         <v>13.4</v>
       </c>
@@ -54966,7 +54970,7 @@
         <v>3.0861588432043039</v>
       </c>
     </row>
-    <row r="152" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C152" s="16">
         <v>13.5</v>
       </c>
@@ -55003,7 +55007,7 @@
         <v>3.0753430853853172</v>
       </c>
     </row>
-    <row r="153" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C153" s="16">
         <v>13.6</v>
       </c>
@@ -55040,7 +55044,7 @@
         <v>3.0646402510648585</v>
       </c>
     </row>
-    <row r="154" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C154" s="16">
         <v>13.7</v>
       </c>
@@ -55077,7 +55081,7 @@
         <v>3.0540483888312293</v>
       </c>
     </row>
-    <row r="155" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C155" s="16">
         <v>13.8</v>
       </c>
@@ -55114,7 +55118,7 @@
         <v>3.0435655941595412</v>
       </c>
     </row>
-    <row r="156" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C156" s="16">
         <v>13.9</v>
       </c>
@@ -55151,7 +55155,7 @@
         <v>3.0331900079731651</v>
       </c>
     </row>
-    <row r="157" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C157" s="16">
         <v>14</v>
       </c>
@@ -55188,7 +55192,7 @@
         <v>3.0229198152587529</v>
       </c>
     </row>
-    <row r="158" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C158" s="16">
         <v>14.1</v>
       </c>
@@ -55225,7 +55229,7 @@
         <v>3.0127532437325004</v>
       </c>
     </row>
-    <row r="159" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C159" s="16">
         <v>14.2</v>
       </c>
@@ -55262,7 +55266,7 @@
         <v>3.0026885625554209</v>
       </c>
     </row>
-    <row r="160" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C160" s="16">
         <v>14.3</v>
       </c>
@@ -55299,7 +55303,7 @@
         <v>2.9927240810955178</v>
       </c>
     </row>
-    <row r="161" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C161" s="16">
         <v>14.4</v>
       </c>
@@ -55336,7 +55340,7 @@
         <v>2.9828581477348415</v>
       </c>
     </row>
-    <row r="162" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C162" s="16">
         <v>14.5</v>
       </c>
@@ -55373,7 +55377,7 @@
         <v>2.9730891487195295</v>
       </c>
     </row>
-    <row r="163" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C163" s="16">
         <v>14.6</v>
       </c>
@@ -55410,7 +55414,7 @@
         <v>2.963415507050998</v>
       </c>
     </row>
-    <row r="164" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C164" s="16">
         <v>14.7</v>
       </c>
@@ -55447,7 +55451,7 @@
         <v>2.9538356814165678</v>
       </c>
     </row>
-    <row r="165" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C165" s="16">
         <v>14.8</v>
       </c>
@@ -55484,7 +55488,7 @@
         <v>2.9443481651578702</v>
       </c>
     </row>
-    <row r="166" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C166" s="16">
         <v>14.9</v>
       </c>
@@ -55521,7 +55525,7 @@
         <v>2.9349514852754708</v>
       </c>
     </row>
-    <row r="167" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C167" s="16">
         <v>15</v>
       </c>
@@ -55558,7 +55562,7 @@
         <v>2.9256442014682116</v>
       </c>
     </row>
-    <row r="168" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C168" s="16">
         <v>15.1</v>
       </c>
@@ -55595,7 +55599,7 @@
         <v>2.9164249052058544</v>
       </c>
     </row>
-    <row r="169" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C169" s="16">
         <v>15.2</v>
       </c>
@@ -55632,7 +55636,7 @@
         <v>2.9072922188336721</v>
       </c>
     </row>
-    <row r="170" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C170" s="16">
         <v>15.3</v>
       </c>
@@ -55669,7 +55673,7 @@
         <v>2.8982447947076828</v>
       </c>
     </row>
-    <row r="171" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C171" s="16">
         <v>15.4</v>
       </c>
@@ -55706,7 +55710,7 @@
         <v>2.8892813143593168</v>
       </c>
     </row>
-    <row r="172" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C172" s="16">
         <v>15.5</v>
       </c>
@@ -55743,7 +55747,7 @@
         <v>2.8804004876883096</v>
       </c>
     </row>
-    <row r="173" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C173" s="16">
         <v>15.6</v>
       </c>
@@ -55780,7 +55784,7 @@
         <v>2.8716010521827351</v>
       </c>
     </row>
-    <row r="174" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C174" s="16">
         <v>15.7</v>
       </c>
@@ -55817,7 +55821,7 @@
         <v>2.8628817721650801</v>
       </c>
     </row>
-    <row r="175" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C175" s="16">
         <v>15.8</v>
       </c>
@@ -55854,7 +55858,7 @@
         <v>2.8542414380633478</v>
       </c>
     </row>
-    <row r="176" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C176" s="16">
         <v>15.9</v>
       </c>
@@ -55891,7 +55895,7 @@
         <v>2.8456788657062178</v>
       </c>
     </row>
-    <row r="177" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C177" s="16">
         <v>16</v>
       </c>
@@ -55928,7 +55932,7 @@
         <v>2.8371928956413286</v>
       </c>
     </row>
-    <row r="178" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C178" s="16">
         <v>16.100000000000001</v>
       </c>
@@ -55965,7 +55969,7 @@
         <v>2.8287823924757856</v>
       </c>
     </row>
-    <row r="179" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C179" s="16">
         <v>16.2</v>
       </c>
@@ -56002,7 +56006,7 @@
         <v>2.8204462442380471</v>
       </c>
     </row>
-    <row r="180" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C180" s="16">
         <v>16.3</v>
       </c>
@@ -56039,7 +56043,7 @@
         <v>2.8121833617603813</v>
       </c>
     </row>
-    <row r="181" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C181" s="16">
         <v>16.399999999999999</v>
       </c>
@@ -56076,7 +56080,7 @@
         <v>2.8039926780810975</v>
       </c>
     </row>
-    <row r="182" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C182" s="16">
         <v>16.5</v>
       </c>
@@ -56113,7 +56117,7 @@
         <v>2.7958731478658287</v>
       </c>
     </row>
-    <row r="183" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C183" s="16">
         <v>16.600000000000001</v>
       </c>
@@ -56150,7 +56154,7 @@
         <v>2.7878237468471339</v>
       </c>
     </row>
-    <row r="184" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C184" s="16">
         <v>16.7</v>
       </c>
@@ -56187,7 +56191,7 @@
         <v>2.7798434712817515</v>
       </c>
     </row>
-    <row r="185" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C185" s="16">
         <v>16.8</v>
       </c>
@@ -56224,7 +56228,7 @@
         <v>2.7719313374248431</v>
       </c>
     </row>
-    <row r="186" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C186" s="16">
         <v>16.899999999999999</v>
       </c>
@@ -56261,7 +56265,7 @@
         <v>2.7640863810206051</v>
       </c>
     </row>
-    <row r="187" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C187" s="16">
         <v>17</v>
       </c>
@@ -56298,7 +56302,7 @@
         <v>2.7563076568086493</v>
       </c>
     </row>
-    <row r="188" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C188" s="16">
         <v>17.100000000000001</v>
       </c>
@@ -56335,7 +56339,7 @@
         <v>2.7485942380455808</v>
       </c>
     </row>
-    <row r="189" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C189" s="16">
         <v>17.2</v>
       </c>
@@ -56372,7 +56376,7 @@
         <v>2.7409452160412173</v>
       </c>
     </row>
-    <row r="190" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C190" s="16">
         <v>17.3</v>
       </c>
@@ -56409,7 +56413,7 @@
         <v>2.7333596997089313</v>
       </c>
     </row>
-    <row r="191" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C191" s="16">
         <v>17.399999999999999</v>
       </c>
@@ -56446,7 +56450,7 @@
         <v>2.7258368151296022</v>
       </c>
     </row>
-    <row r="192" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C192" s="16">
         <v>17.5</v>
       </c>
@@ -56483,7 +56487,7 @@
         <v>2.7183757051286999</v>
       </c>
     </row>
-    <row r="193" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C193" s="16">
         <v>17.600000000000001</v>
       </c>
@@ -56520,7 +56524,7 @@
         <v>2.7109755288660313</v>
       </c>
     </row>
-    <row r="194" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C194" s="16">
         <v>17.7</v>
       </c>
@@ -56557,7 +56561,7 @@
         <v>2.7036354614377052</v>
       </c>
     </row>
-    <row r="195" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C195" s="16">
         <v>17.8</v>
       </c>
@@ -56594,7 +56598,7 @@
         <v>2.6963546934898912</v>
       </c>
     </row>
-    <row r="196" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C196" s="16">
         <v>17.899999999999999</v>
       </c>
@@ -56631,7 +56635,7 @@
         <v>2.6891324308439528</v>
       </c>
     </row>
-    <row r="197" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="197" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C197" s="16">
         <v>18</v>
       </c>
@@ -56668,7 +56672,7 @@
         <v>2.6819678941325735</v>
       </c>
     </row>
-    <row r="198" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C198" s="16">
         <v>18.100000000000001</v>
       </c>
@@ -56705,7 +56709,7 @@
         <v>2.6748603184464859</v>
       </c>
     </row>
-    <row r="199" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C199" s="16">
         <v>18.2</v>
       </c>
@@ -56742,7 +56746,7 @@
         <v>2.6678089529914439</v>
       </c>
     </row>
-    <row r="200" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="200" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C200" s="16">
         <v>18.3</v>
       </c>
@@ -56779,7 +56783,7 @@
         <v>2.6608130607550975</v>
       </c>
     </row>
-    <row r="201" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="201" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C201" s="16">
         <v>18.399999999999999</v>
       </c>
@@ -56816,7 +56820,7 @@
         <v>2.6538719181834161</v>
       </c>
     </row>
-    <row r="202" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C202" s="16">
         <v>18.5</v>
       </c>
@@ -56853,7 +56857,7 @@
         <v>2.6469848148663577</v>
       </c>
     </row>
-    <row r="203" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="203" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C203" s="16">
         <v>18.600000000000001</v>
       </c>
@@ -56890,7 +56894,7 @@
         <v>2.6401510532324592</v>
       </c>
     </row>
-    <row r="204" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="204" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C204" s="16">
         <v>18.7</v>
       </c>
@@ -56927,7 +56931,7 @@
         <v>2.6333699482520578</v>
       </c>
     </row>
-    <row r="205" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="205" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C205" s="16">
         <v>18.8</v>
       </c>
@@ -56964,7 +56968,7 @@
         <v>2.6266408271488544</v>
       </c>
     </row>
-    <row r="206" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="206" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C206" s="16">
         <v>18.899999999999999</v>
       </c>
@@ -57001,7 +57005,7 @@
         <v>2.6199630291195439</v>
       </c>
     </row>
-    <row r="207" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="207" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C207" s="16">
         <v>19</v>
       </c>
@@ -57038,7 +57042,7 @@
         <v>2.6133359050612439</v>
       </c>
     </row>
-    <row r="208" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="208" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C208" s="16">
         <v>19.100000000000001</v>
       </c>
@@ -57075,7 +57079,7 @@
         <v>2.6067588173064733</v>
       </c>
     </row>
-    <row r="209" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="209" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C209" s="16">
         <v>19.2</v>
       </c>
@@ -57112,7 +57116,7 @@
         <v>2.6002311393654267</v>
       </c>
     </row>
-    <row r="210" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="210" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C210" s="16">
         <v>19.3</v>
       </c>
@@ -57149,7 +57153,7 @@
         <v>2.5937522556753181</v>
       </c>
     </row>
-    <row r="211" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="211" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C211" s="16">
         <v>19.399999999999999</v>
       </c>
@@ -57186,7 +57190,7 @@
         <v>2.5873215613565534</v>
       </c>
     </row>
-    <row r="212" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="212" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C212" s="16">
         <v>19.5</v>
       </c>
@@ -57223,7 +57227,7 @@
         <v>2.5809384619755287</v>
       </c>
     </row>
-    <row r="213" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="213" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C213" s="16">
         <v>19.600000000000001</v>
       </c>
@@ -57260,7 +57264,7 @@
         <v>2.5746023733138252</v>
       </c>
     </row>
-    <row r="214" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="214" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C214" s="16">
         <v>19.7</v>
       </c>
@@ -57297,7 +57301,7 @@
         <v>2.5683127211436125</v>
       </c>
     </row>
-    <row r="215" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="215" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C215" s="16">
         <v>19.8</v>
       </c>
@@ -57334,7 +57338,7 @@
         <v>2.5620689410090574</v>
       </c>
     </row>
-    <row r="216" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C216" s="16">
         <v>19.899999999999999</v>
       </c>
@@ -57371,7 +57375,7 @@
         <v>2.5558704780135448</v>
       </c>
     </row>
-    <row r="217" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="217" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C217" s="16">
         <v>20</v>
       </c>
@@ -57408,7 +57412,7 @@
         <v>2.5497167866125441</v>
       </c>
     </row>
-    <row r="218" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C218" s="16">
         <v>20.100000000000001</v>
       </c>
@@ -57445,7 +57449,7 @@
         <v>2.5436073304119229</v>
       </c>
     </row>
-    <row r="219" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C219" s="16">
         <v>20.2</v>
       </c>
@@ -57482,7 +57486,7 @@
         <v>2.5375415819715608</v>
       </c>
     </row>
-    <row r="220" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="220" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C220" s="16">
         <v>20.3</v>
       </c>
@@ -57519,7 +57523,7 @@
         <v>2.5315190226140878</v>
       </c>
     </row>
-    <row r="221" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C221" s="16">
         <v>20.399999999999999</v>
       </c>
@@ -57556,7 +57560,7 @@
         <v>2.5255391422385864</v>
       </c>
     </row>
-    <row r="222" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="222" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C222" s="16">
         <v>20.5</v>
       </c>
@@ -57593,7 +57597,7 @@
         <v>2.5196014391391239</v>
       </c>
     </row>
-    <row r="223" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="223" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C223" s="16">
         <v>20.6</v>
       </c>
@@ -57630,7 +57634,7 @@
         <v>2.5137054198279438</v>
       </c>
     </row>
-    <row r="224" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="224" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C224" s="16">
         <v>20.7</v>
       </c>
@@ -57667,7 +57671,7 @@
         <v>2.5078505988631932</v>
       </c>
     </row>
-    <row r="225" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="225" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C225" s="16">
         <v>20.8</v>
       </c>
@@ -57704,7 +57708,7 @@
         <v>2.5020364986810444</v>
       </c>
     </row>
-    <row r="226" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C226" s="16">
         <v>20.9</v>
       </c>
@@ -57741,7 +57745,7 @@
         <v>2.4962626494320741</v>
       </c>
     </row>
-    <row r="227" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C227" s="16">
         <v>21</v>
       </c>
@@ -57778,7 +57782,7 @@
         <v>2.4905285888217783</v>
       </c>
     </row>
-    <row r="228" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="228" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C228" s="16">
         <v>21.1</v>
       </c>
@@ -57815,7 +57819,7 @@
         <v>2.484833861955102</v>
       </c>
     </row>
-    <row r="229" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C229" s="16">
         <v>21.2</v>
       </c>
@@ -57852,7 +57856,7 @@
         <v>2.4791780211848562</v>
       </c>
     </row>
-    <row r="230" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C230" s="16">
         <v>21.3</v>
       </c>
@@ -57889,7 +57893,7 @@
         <v>2.4735606259639176</v>
       </c>
     </row>
-    <row r="231" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C231" s="16">
         <v>21.4</v>
       </c>
@@ -57926,7 +57930,7 @@
         <v>2.4679812427010908</v>
       </c>
     </row>
-    <row r="232" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C232" s="16">
         <v>21.5</v>
       </c>
@@ -57963,7 +57967,7 @@
         <v>2.4624394446205353</v>
       </c>
     </row>
-    <row r="233" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C233" s="16">
         <v>21.6</v>
       </c>
@@ -58000,7 +58004,7 @@
         <v>2.456934811624647</v>
       </c>
     </row>
-    <row r="234" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C234" s="16">
         <v>21.7</v>
       </c>
@@ -58037,7 +58041,7 @@
         <v>2.4514669301602967</v>
       </c>
     </row>
-    <row r="235" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C235" s="16">
         <v>21.8</v>
       </c>
@@ -58074,7 +58078,7 @@
         <v>2.4460353930883278</v>
       </c>
     </row>
-    <row r="236" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C236" s="16">
         <v>21.9</v>
       </c>
@@ -58111,7 +58115,7 @@
         <v>2.440639799556223</v>
       </c>
     </row>
-    <row r="237" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C237" s="16">
         <v>22</v>
       </c>
@@ -58148,7 +58152,7 @@
         <v>2.4352797548738416</v>
       </c>
     </row>
-    <row r="238" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C238" s="16">
         <v>22.1</v>
       </c>
@@ -58185,7 +58189,7 @@
         <v>2.4299548703921565</v>
       </c>
     </row>
-    <row r="239" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C239" s="16">
         <v>22.2</v>
       </c>
@@ -58222,7 +58226,7 @@
         <v>2.4246647633848801</v>
       </c>
     </row>
-    <row r="240" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C240" s="16">
         <v>22.3</v>
       </c>
@@ -58259,7 +58263,7 @@
         <v>2.4194090569329272</v>
       </c>
     </row>
-    <row r="241" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="241" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C241" s="16">
         <v>22.4</v>
       </c>
@@ -58296,7 +58300,7 @@
         <v>2.4141873798116102</v>
       </c>
     </row>
-    <row r="242" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="242" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C242" s="16">
         <v>22.5</v>
       </c>
@@ -58333,7 +58337,7 @@
         <v>2.4089993663805074</v>
       </c>
     </row>
-    <row r="243" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="243" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C243" s="16">
         <v>22.6</v>
       </c>
@@ -58370,7 +58374,7 @@
         <v>2.4038446564759197</v>
       </c>
     </row>
-    <row r="244" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="244" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C244" s="16">
         <v>22.7</v>
       </c>
@@ -58407,7 +58411,7 @@
         <v>2.3987228953058493</v>
       </c>
     </row>
-    <row r="245" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="245" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C245" s="16">
         <v>22.8</v>
       </c>
@@ -58444,7 +58448,7 @@
         <v>2.393633733347432</v>
       </c>
     </row>
-    <row r="246" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="246" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C246" s="16">
         <v>22.9</v>
       </c>
@@ -58481,7 +58485,7 @@
         <v>2.3885768262467457</v>
       </c>
     </row>
-    <row r="247" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="247" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C247" s="16">
         <v>23</v>
       </c>
@@ -58518,7 +58522,7 @@
         <v>2.3835518347209472</v>
       </c>
     </row>
-    <row r="248" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="248" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C248" s="16">
         <v>23.1</v>
       </c>
@@ -58555,7 +58559,7 @@
         <v>2.3785584244626548</v>
       </c>
     </row>
-    <row r="249" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="249" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C249" s="16">
         <v>23.2</v>
       </c>
@@ -58592,7 +58596,7 @@
         <v>2.3735962660465328</v>
       </c>
     </row>
-    <row r="250" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="250" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C250" s="16">
         <v>23.3</v>
       </c>
@@ -58629,7 +58633,7 @@
         <v>2.3686650348380063</v>
       </c>
     </row>
-    <row r="251" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="251" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C251" s="16">
         <v>23.4</v>
       </c>
@@ -58666,7 +58670,7 @@
         <v>2.363764410904055</v>
       </c>
     </row>
-    <row r="252" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="252" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C252" s="16">
         <v>23.5</v>
       </c>
@@ -58703,7 +58707,7 @@
         <v>2.3588940789260282</v>
       </c>
     </row>
-    <row r="253" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="253" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C253" s="16">
         <v>23.6</v>
       </c>
@@ -58740,7 +58744,7 @@
         <v>2.3540537281144283</v>
       </c>
     </row>
-    <row r="254" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="254" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C254" s="16">
         <v>23.7</v>
       </c>
@@ -58777,7 +58781,7 @@
         <v>2.3492430521256114</v>
       </c>
     </row>
-    <row r="255" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="255" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C255" s="16">
         <v>23.8</v>
       </c>
@@ -58814,7 +58818,7 @@
         <v>2.3444617489803479</v>
       </c>
     </row>
-    <row r="256" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C256" s="16">
         <v>23.9</v>
       </c>
@@ -58851,7 +58855,7 @@
         <v>2.3397095209842051</v>
       </c>
     </row>
-    <row r="257" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="257" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C257" s="16">
         <v>24</v>
       </c>
@@ -58888,7 +58892,7 @@
         <v>2.3349860746496933</v>
       </c>
     </row>
-    <row r="258" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="258" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C258" s="16">
         <v>24.1</v>
       </c>
@@ -58925,7 +58929,7 @@
         <v>2.3302911206201369</v>
       </c>
     </row>
-    <row r="259" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="259" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C259" s="16">
         <v>24.2</v>
       </c>
@@ -58962,7 +58966,7 @@
         <v>2.3256243735952205</v>
       </c>
     </row>
-    <row r="260" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="260" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C260" s="16">
         <v>24.3</v>
       </c>
@@ -58999,7 +59003,7 @@
         <v>2.3209855522581671</v>
       </c>
     </row>
-    <row r="261" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C261" s="16">
         <v>24.4</v>
       </c>
@@ -59036,7 +59040,7 @@
         <v>2.3163743792045151</v>
       </c>
     </row>
-    <row r="262" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="262" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C262" s="16">
         <v>24.5</v>
       </c>
@@ -59073,7 +59077,7 @@
         <v>2.3117905808724357</v>
       </c>
     </row>
-    <row r="263" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="263" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C263" s="16">
         <v>24.6</v>
       </c>
@@ -59110,7 +59114,7 @@
         <v>2.3072338874745681</v>
       </c>
     </row>
-    <row r="264" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="264" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C264" s="16">
         <v>24.7</v>
       </c>
@@ -59147,7 +59151,7 @@
         <v>2.3027040329313246</v>
       </c>
     </row>
-    <row r="265" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="265" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C265" s="16">
         <v>24.8</v>
       </c>
@@ -59184,7 +59188,7 @@
         <v>2.2982007548056296</v>
       </c>
     </row>
-    <row r="266" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="266" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C266" s="16">
         <v>24.9</v>
       </c>
@@ -59221,7 +59225,7 @@
         <v>2.2937237942390598</v>
       </c>
     </row>
-    <row r="267" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="267" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C267" s="16">
         <v>25</v>
       </c>
@@ -59258,7 +59262,7 @@
         <v>2.2892728958893431</v>
       </c>
     </row>
-    <row r="268" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="268" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C268" s="16">
         <v>25.1</v>
       </c>
@@ -59295,7 +59299,7 @@
         <v>2.2848478078691925</v>
       </c>
     </row>
-    <row r="269" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="269" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C269" s="16">
         <v>25.2</v>
       </c>
@@ -59332,7 +59336,7 @@
         <v>2.2804482816864278</v>
       </c>
     </row>
-    <row r="270" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="270" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C270" s="16">
         <v>25.3</v>
       </c>
@@ -59369,7 +59373,7 @@
         <v>2.2760740721853687</v>
       </c>
     </row>
-    <row r="271" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C271" s="16">
         <v>25.4</v>
       </c>
@@ -59406,7 +59410,7 @@
         <v>2.2717249374894544</v>
       </c>
     </row>
-    <row r="272" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="272" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C272" s="16">
         <v>25.5</v>
       </c>
@@ -59443,7 +59447,7 @@
         <v>2.2674006389450665</v>
       </c>
     </row>
-    <row r="273" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C273" s="16">
         <v>25.6</v>
       </c>
@@ -59480,7 +59484,7 @@
         <v>2.263100941066523</v>
       </c>
     </row>
-    <row r="274" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C274" s="16">
         <v>25.7</v>
       </c>
@@ -59517,7 +59521,7 @@
         <v>2.2588256114822163</v>
       </c>
     </row>
-    <row r="275" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C275" s="16">
         <v>25.8</v>
       </c>
@@ -59554,7 +59558,7 @@
         <v>2.2545744208818674</v>
       </c>
     </row>
-    <row r="276" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C276" s="16">
         <v>25.9</v>
       </c>
@@ -59591,7 +59595,7 @@
         <v>2.2503471429648636</v>
       </c>
     </row>
-    <row r="277" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C277" s="16">
         <v>26</v>
       </c>
@@ -59628,7 +59632,7 @@
         <v>2.2461435543896626</v>
       </c>
     </row>
-    <row r="278" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C278" s="16">
         <v>26.1</v>
       </c>
@@ -59665,7 +59669,7 @@
         <v>2.241963434724231</v>
       </c>
     </row>
-    <row r="279" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C279" s="16">
         <v>26.2</v>
       </c>
@@ -59702,7 +59706,7 @@
         <v>2.2378065663974889</v>
       </c>
     </row>
-    <row r="280" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="280" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C280" s="16">
         <v>26.3</v>
       </c>
@@ -59739,7 +59743,7 @@
         <v>2.2336727346517509</v>
       </c>
     </row>
-    <row r="281" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="281" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C281" s="16">
         <v>26.4</v>
       </c>
@@ -59776,7 +59780,7 @@
         <v>2.229561727496121</v>
       </c>
     </row>
-    <row r="282" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="282" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C282" s="16">
         <v>26.5</v>
       </c>
@@ -59813,7 +59817,7 @@
         <v>2.2254733356608298</v>
       </c>
     </row>
-    <row r="283" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C283" s="16">
         <v>26.6</v>
       </c>
@@ -59850,7 +59854,7 @@
         <v>2.221407352552494</v>
       </c>
     </row>
-    <row r="284" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C284" s="16">
         <v>26.7</v>
       </c>
@@ -59887,7 +59891,7 @@
         <v>2.2173635742102658</v>
       </c>
     </row>
-    <row r="285" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C285" s="16">
         <v>26.8</v>
       </c>
@@ -59924,7 +59928,7 @@
         <v>2.2133417992628583</v>
       </c>
     </row>
-    <row r="286" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C286" s="16">
         <v>26.9</v>
       </c>
@@ -59961,7 +59965,7 @@
         <v>2.2093418288864304</v>
       </c>
     </row>
-    <row r="287" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C287" s="16">
         <v>27</v>
       </c>
@@ -59998,7 +60002,7 @@
         <v>2.2053634667632993</v>
       </c>
     </row>
-    <row r="288" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C288" s="16">
         <v>27.1</v>
       </c>
@@ -60035,7 +60039,7 @@
         <v>2.2014065190414707</v>
       </c>
     </row>
-    <row r="289" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C289" s="16">
         <v>27.2</v>
       </c>
@@ -60072,7 +60076,7 @@
         <v>2.1974707942949658</v>
       </c>
     </row>
-    <row r="290" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C290" s="16">
         <v>27.3</v>
       </c>
@@ -60109,7 +60113,7 @@
         <v>2.1935561034849242</v>
       </c>
     </row>
-    <row r="291" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C291" s="16">
         <v>27.4</v>
       </c>
@@ -60146,7 +60150,7 @@
         <v>2.1896622599214668</v>
       </c>
     </row>
-    <row r="292" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C292" s="16">
         <v>27.5</v>
       </c>
@@ -60183,7 +60187,7 @@
         <v>2.1857890792263017</v>
       </c>
     </row>
-    <row r="293" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C293" s="16">
         <v>27.6</v>
       </c>
@@ -60220,7 +60224,7 @@
         <v>2.1819363792960509</v>
       </c>
     </row>
-    <row r="294" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C294" s="16">
         <v>27.7</v>
       </c>
@@ -60257,7 +60261,7 @@
         <v>2.1781039802662936</v>
       </c>
     </row>
-    <row r="295" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C295" s="16">
         <v>27.8</v>
       </c>
@@ -60294,7 +60298,7 @@
         <v>2.1742917044762948</v>
       </c>
     </row>
-    <row r="296" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C296" s="16">
         <v>27.9</v>
       </c>
@@ -60331,7 +60335,7 @@
         <v>2.170499376434412</v>
       </c>
     </row>
-    <row r="297" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C297" s="16">
         <v>28</v>
       </c>
@@ -60368,7 +60372,7 @@
         <v>2.1667268227841654</v>
       </c>
     </row>
-    <row r="298" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C298" s="16">
         <v>28.1</v>
       </c>
@@ -60405,7 +60409,7 @@
         <v>2.1629738722709528</v>
       </c>
     </row>
-    <row r="299" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C299" s="16">
         <v>28.2</v>
       </c>
@@ -60442,7 +60446,7 @@
         <v>2.1592403557093975</v>
       </c>
     </row>
-    <row r="300" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C300" s="16">
         <v>28.3</v>
       </c>
@@ -60479,7 +60483,7 @@
         <v>2.1555261059513127</v>
       </c>
     </row>
-    <row r="301" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C301" s="16">
         <v>28.4</v>
       </c>
@@ -60516,7 +60520,7 @@
         <v>2.1518309578542718</v>
       </c>
     </row>
-    <row r="302" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C302" s="16">
         <v>28.5</v>
       </c>
@@ -60553,7 +60557,7 @@
         <v>2.1481547482507675</v>
       </c>
     </row>
-    <row r="303" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C303" s="16">
         <v>28.6</v>
       </c>
@@ -60590,7 +60594,7 @@
         <v>2.1444973159179512</v>
       </c>
     </row>
-    <row r="304" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="304" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C304" s="16">
         <v>28.7</v>
       </c>
@@ -60627,7 +60631,7 @@
         <v>2.1408585015479327</v>
       </c>
     </row>
-    <row r="305" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C305" s="16">
         <v>28.8</v>
       </c>
@@ -60664,7 +60668,7 @@
         <v>2.137238147718636</v>
       </c>
     </row>
-    <row r="306" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C306" s="16">
         <v>28.9</v>
       </c>
@@ -60701,7 +60705,7 @@
         <v>2.1336360988651957</v>
       </c>
     </row>
-    <row r="307" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C307" s="16">
         <v>29</v>
       </c>
@@ -60738,7 +60742,7 @@
         <v>2.1300522012518814</v>
       </c>
     </row>
-    <row r="308" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="308" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C308" s="16">
         <v>29.1</v>
       </c>
@@ -60775,7 +60779,7 @@
         <v>2.1264863029445351</v>
       </c>
     </row>
-    <row r="309" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="309" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C309" s="16">
         <v>29.2</v>
       </c>
@@ -60812,7 +60816,7 @@
         <v>2.1229382537835191</v>
       </c>
     </row>
-    <row r="310" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C310" s="16">
         <v>29.3</v>
       </c>
@@ -60849,7 +60853,7 @@
         <v>2.1194079053571606</v>
       </c>
     </row>
-    <row r="311" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C311" s="16">
         <v>29.4</v>
       </c>
@@ -60886,7 +60890,7 @@
         <v>2.1158951109756723</v>
       </c>
     </row>
-    <row r="312" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C312" s="16">
         <v>29.5</v>
       </c>
@@ -60923,7 +60927,7 @@
         <v>2.1123997256455556</v>
       </c>
     </row>
-    <row r="313" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="313" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C313" s="16">
         <v>29.6</v>
       </c>
@@ -60960,7 +60964,7 @@
         <v>2.1089216060444618</v>
       </c>
     </row>
-    <row r="314" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="314" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C314" s="16">
         <v>29.7</v>
       </c>
@@ -60997,7 +61001,7 @@
         <v>2.1054606104965106</v>
       </c>
     </row>
-    <row r="315" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="315" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C315" s="16">
         <v>29.8</v>
       </c>
@@ -61034,7 +61038,7 @@
         <v>2.1020165989480488</v>
       </c>
     </row>
-    <row r="316" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="316" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C316" s="16">
         <v>29.9</v>
       </c>
@@ -61071,7 +61075,7 @@
         <v>2.0985894329438488</v>
       </c>
     </row>
-    <row r="317" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="317" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C317" s="16">
         <v>30</v>
       </c>
@@ -61108,7 +61112,7 @@
         <v>2.0951789756037269</v>
       </c>
     </row>
-    <row r="318" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="318" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C318" s="16">
         <v>30.1</v>
       </c>
@@ -61145,7 +61149,7 @@
         <v>2.0917850915995855</v>
       </c>
     </row>
-    <row r="319" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="319" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C319" s="16">
         <v>30.2</v>
       </c>
@@ -61182,7 +61186,7 @@
         <v>2.0884076471328528</v>
       </c>
     </row>
-    <row r="320" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="320" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C320" s="16">
         <v>30.3</v>
       </c>
@@ -61219,7 +61223,7 @@
         <v>2.0850465099123339</v>
       </c>
     </row>
-    <row r="321" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="321" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C321" s="16">
         <v>30.4</v>
       </c>
@@ -61256,7 +61260,7 @@
         <v>2.0817015491324424</v>
       </c>
     </row>
-    <row r="322" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="322" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C322" s="16">
         <v>30.5</v>
       </c>
@@ -61293,7 +61297,7 @@
         <v>2.0783726354518208</v>
       </c>
     </row>
-    <row r="323" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="323" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C323" s="16">
         <v>30.6</v>
       </c>
@@ -61330,7 +61334,7 @@
         <v>2.0750596409723352</v>
       </c>
     </row>
-    <row r="324" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="324" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C324" s="16">
         <v>30.7</v>
       </c>
@@ -61367,7 +61371,7 @@
         <v>2.0717624392184342</v>
       </c>
     </row>
-    <row r="325" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="325" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C325" s="16">
         <v>30.8</v>
       </c>
@@ -61404,7 +61408,7 @@
         <v>2.0684809051168704</v>
       </c>
     </row>
-    <row r="326" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="326" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C326" s="16">
         <v>30.9</v>
       </c>
@@ -61441,7 +61445,7 @@
         <v>2.0652149149767727</v>
       </c>
     </row>
-    <row r="327" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="327" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C327" s="16">
         <v>31</v>
       </c>
@@ -61478,7 +61482,7 @@
         <v>2.0619643464700652</v>
       </c>
     </row>
-    <row r="328" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="328" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C328" s="16">
         <v>31.1</v>
       </c>
@@ -61515,7 +61519,7 @@
         <v>2.0587290786122217</v>
       </c>
     </row>
-    <row r="329" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="329" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C329" s="16">
         <v>31.2</v>
       </c>
@@ -61552,7 +61556,7 @@
         <v>2.0555089917433516</v>
       </c>
     </row>
-    <row r="330" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="330" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C330" s="16">
         <v>31.3</v>
       </c>
@@ -61589,7 +61593,7 @@
         <v>2.0523039675096135</v>
       </c>
     </row>
-    <row r="331" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="331" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C331" s="16">
         <v>31.4</v>
       </c>
@@ -61626,7 +61630,7 @@
         <v>2.0491138888449423</v>
       </c>
     </row>
-    <row r="332" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="332" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C332" s="16">
         <v>31.5</v>
       </c>
@@ -61663,7 +61667,7 @@
         <v>2.0459386399530901</v>
       </c>
     </row>
-    <row r="333" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="333" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C333" s="16">
         <v>31.6</v>
       </c>
@@ -61700,7 +61704,7 @@
         <v>2.042778106289973</v>
       </c>
     </row>
-    <row r="334" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="334" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C334" s="16">
         <v>31.7</v>
       </c>
@@ -61737,7 +61741,7 @@
         <v>2.039632174546314</v>
       </c>
     </row>
-    <row r="335" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="335" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C335" s="16">
         <v>31.8</v>
       </c>
@@ -61774,7 +61778,7 @@
         <v>2.0365007326305813</v>
       </c>
     </row>
-    <row r="336" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="336" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C336" s="16">
         <v>31.9</v>
       </c>
@@ -61811,7 +61815,7 @@
         <v>2.0333836696522143</v>
       </c>
     </row>
-    <row r="337" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="337" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C337" s="16">
         <v>32</v>
       </c>
@@ -61848,7 +61852,7 @@
         <v>2.0302808759051292</v>
       </c>
     </row>
-    <row r="338" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="338" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C338" s="16">
         <v>32.1</v>
       </c>
@@ -61885,7 +61889,7 @@
         <v>2.0271922428515023</v>
       </c>
     </row>
-    <row r="339" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="339" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C339" s="16">
         <v>32.200000000000003</v>
       </c>
@@ -61922,7 +61926,7 @@
         <v>2.0241176631058231</v>
       </c>
     </row>
-    <row r="340" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="340" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C340" s="16">
         <v>32.299999999999997</v>
       </c>
@@ -61959,7 +61963,7 @@
         <v>2.0210570304192119</v>
       </c>
     </row>
-    <row r="341" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="341" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C341" s="16">
         <v>32.4</v>
       </c>
@@ -61996,7 +62000,7 @@
         <v>2.0180102396639996</v>
       </c>
     </row>
-    <row r="342" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="342" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C342" s="16">
         <v>32.5</v>
       </c>
@@ -62033,7 +62037,7 @@
         <v>2.0149771868185606</v>
       </c>
     </row>
-    <row r="343" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="343" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C343" s="16">
         <v>32.6</v>
       </c>
@@ -62070,7 +62074,7 @@
         <v>2.0119577689523958</v>
       </c>
     </row>
-    <row r="344" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="344" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C344" s="16">
         <v>32.700000000000003</v>
       </c>
@@ -62107,7 +62111,7 @@
         <v>2.0089518842114611</v>
       </c>
     </row>
-    <row r="345" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="345" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C345" s="16">
         <v>32.799999999999997</v>
       </c>
@@ -62144,7 +62148,7 @@
         <v>2.0059594318037384</v>
       </c>
     </row>
-    <row r="346" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="346" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C346" s="16">
         <v>32.9</v>
       </c>
@@ -62181,7 +62185,7 @@
         <v>2.0029803119850373</v>
       </c>
     </row>
-    <row r="347" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="347" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C347" s="16">
         <v>33</v>
       </c>
@@ -62218,7 +62222,7 @@
         <v>2.0000144260450332</v>
       </c>
     </row>
-    <row r="348" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="348" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C348" s="16">
         <v>33.1</v>
       </c>
@@ -62255,7 +62259,7 @@
         <v>1.9970616762935292</v>
       </c>
     </row>
-    <row r="349" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="349" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C349" s="16">
         <v>33.200000000000003</v>
       </c>
@@ -62292,7 +62296,7 @@
         <v>1.9941219660469416</v>
       </c>
     </row>
-    <row r="350" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="350" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C350" s="16">
         <v>33.299999999999997</v>
       </c>
@@ -62329,7 +62333,7 @@
         <v>1.991195199615003</v>
       </c>
     </row>
-    <row r="351" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="351" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C351" s="16">
         <v>33.4</v>
       </c>
@@ -62366,7 +62370,7 @@
         <v>1.9882812822876799</v>
       </c>
     </row>
-    <row r="352" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="352" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C352" s="16">
         <v>33.5</v>
       </c>
@@ -62403,7 +62407,7 @@
         <v>1.9853801203222992</v>
       </c>
     </row>
-    <row r="353" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="353" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C353" s="16">
         <v>33.6</v>
       </c>
@@ -62440,7 +62444,7 @@
         <v>1.9824916209308838</v>
       </c>
     </row>
-    <row r="354" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="354" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C354" s="16">
         <v>33.700000000000003</v>
       </c>
@@ -62477,7 +62481,7 @@
         <v>1.9796156922676853</v>
       </c>
     </row>
-    <row r="355" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="355" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C355" s="16">
         <v>33.799999999999997</v>
       </c>
@@ -62514,7 +62518,7 @@
         <v>1.9767522434169198</v>
       </c>
     </row>
-    <row r="356" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="356" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C356" s="16">
         <v>33.9</v>
       </c>
@@ -62551,7 +62555,7 @@
         <v>1.9739011843806957</v>
       </c>
     </row>
-    <row r="357" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="357" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C357" s="16">
         <v>34</v>
       </c>
@@ -62588,7 +62592,7 @@
         <v>1.9710624260671334</v>
       </c>
     </row>
-    <row r="358" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="358" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C358" s="16">
         <v>34.1</v>
       </c>
@@ -62625,7 +62629,7 @@
         <v>1.9682358802786715</v>
       </c>
     </row>
-    <row r="359" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="359" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C359" s="16">
         <v>34.200000000000003</v>
       </c>
@@ -62662,7 +62666,7 @@
         <v>1.9654214597005579</v>
       </c>
     </row>
-    <row r="360" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="360" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C360" s="16">
         <v>34.299999999999997</v>
       </c>
@@ -62699,7 +62703,7 @@
         <v>1.9626190778895218</v>
       </c>
     </row>
-    <row r="361" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="361" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C361" s="16">
         <v>34.4</v>
       </c>
@@ -62736,7 +62740,7 @@
         <v>1.9598286492626205</v>
       </c>
     </row>
-    <row r="362" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="362" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C362" s="16">
         <v>34.5</v>
       </c>
@@ -62773,7 +62777,7 @@
         <v>1.9570500890862632</v>
       </c>
     </row>
-    <row r="363" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="363" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C363" s="16">
         <v>34.6</v>
       </c>
@@ -62810,7 +62814,7 @@
         <v>1.9542833134654036</v>
       </c>
     </row>
-    <row r="364" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="364" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C364" s="16">
         <v>34.700000000000003</v>
       </c>
@@ -62847,7 +62851,7 @@
         <v>1.9515282393329003</v>
       </c>
     </row>
-    <row r="365" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="365" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C365" s="16">
         <v>34.799999999999997</v>
       </c>
@@ -62884,7 +62888,7 @@
         <v>1.9487847844390422</v>
       </c>
     </row>
-    <row r="366" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="366" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C366" s="16">
         <v>34.9</v>
       </c>
@@ -62921,7 +62925,7 @@
         <v>1.9460528673412349</v>
       </c>
     </row>
-    <row r="367" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="367" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C367" s="16">
         <v>35</v>
       </c>
@@ -62958,7 +62962,7 @@
         <v>1.9433324073938472</v>
       </c>
     </row>
-    <row r="368" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="368" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C368" s="16">
         <v>35.1</v>
       </c>
@@ -62995,7 +62999,7 @@
         <v>1.9406233247382103</v>
       </c>
     </row>
-    <row r="369" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="369" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C369" s="16">
         <v>35.200000000000003</v>
       </c>
@@ -63032,7 +63036,7 @@
         <v>1.9379255402927726</v>
       </c>
     </row>
-    <row r="370" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="370" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C370" s="16">
         <v>35.299999999999997</v>
       </c>
@@ -63069,7 +63073,7 @@
         <v>1.9352389757434048</v>
       </c>
     </row>
-    <row r="371" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="371" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C371" s="16">
         <v>35.4</v>
       </c>
@@ -63106,7 +63110,7 @@
         <v>1.932563553533849</v>
       </c>
     </row>
-    <row r="372" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="372" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C372" s="16">
         <v>35.5</v>
       </c>
@@ -63143,7 +63147,7 @@
         <v>1.9298991968563175</v>
       </c>
     </row>
-    <row r="373" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="373" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C373" s="16">
         <v>35.6</v>
       </c>
@@ -63180,7 +63184,7 @@
         <v>1.9272458296422297</v>
       </c>
     </row>
-    <row r="374" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="374" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C374" s="16">
         <v>35.700000000000003</v>
       </c>
@@ -63217,7 +63221,7 @@
         <v>1.9246033765530906</v>
       </c>
     </row>
-    <row r="375" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="375" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C375" s="16">
         <v>35.799999999999997</v>
       </c>
@@ -63254,7 +63258,7 @@
         <v>1.9219717629715072</v>
       </c>
     </row>
-    <row r="376" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="376" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C376" s="16">
         <v>35.9</v>
       </c>
@@ -63291,7 +63295,7 @@
         <v>1.9193509149923376</v>
       </c>
     </row>
-    <row r="377" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="377" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C377" s="16">
         <v>36</v>
       </c>
@@ -63328,7 +63332,7 @@
         <v>1.9167407594139736</v>
       </c>
     </row>
-    <row r="378" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="378" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C378" s="16">
         <v>36.1</v>
       </c>
@@ -63365,7 +63369,7 @@
         <v>1.9141412237297544</v>
       </c>
     </row>
-    <row r="379" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="379" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C379" s="16">
         <v>36.200000000000003</v>
       </c>
@@ -63402,7 +63406,7 @@
         <v>1.9115522361195056</v>
       </c>
     </row>
-    <row r="380" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="380" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C380" s="16">
         <v>36.299999999999997</v>
       </c>
@@ -63439,7 +63443,7 @@
         <v>1.9089737254412058</v>
       </c>
     </row>
-    <row r="381" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="381" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C381" s="16">
         <v>36.4</v>
       </c>
@@ -63476,7 +63480,7 @@
         <v>1.9064056212227762</v>
       </c>
     </row>
-    <row r="382" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="382" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C382" s="16">
         <v>36.5</v>
       </c>
@@ -63513,7 +63517,7 @@
         <v>1.9038478536539907</v>
       </c>
     </row>
-    <row r="383" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="383" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C383" s="16">
         <v>36.6</v>
       </c>
@@ -63550,7 +63554,7 @@
         <v>1.9013003535785042</v>
       </c>
     </row>
-    <row r="384" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="384" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C384" s="16">
         <v>36.700000000000003</v>
       </c>
@@ -63587,7 +63591,7 @@
         <v>1.8987630524860013</v>
       </c>
     </row>
-    <row r="385" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="385" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C385" s="16">
         <v>36.799999999999997</v>
       </c>
@@ -63624,7 +63628,7 @@
         <v>1.8962358825044565</v>
       </c>
     </row>
-    <row r="386" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="386" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C386" s="16">
         <v>36.9</v>
       </c>
@@ -63661,7 +63665,7 @@
         <v>1.8937187763925083</v>
       </c>
     </row>
-    <row r="387" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="387" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C387" s="16">
         <v>37</v>
       </c>
@@ -63698,7 +63702,7 @@
         <v>1.8912116675319457</v>
       </c>
     </row>
-    <row r="388" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="388" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C388" s="16">
         <v>37.1</v>
       </c>
@@ -63735,7 +63739,7 @@
         <v>1.8887144899203023</v>
       </c>
     </row>
-    <row r="389" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="389" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C389" s="16">
         <v>37.200000000000003</v>
       </c>
@@ -63772,7 +63776,7 @@
         <v>1.8862271781635582</v>
       </c>
     </row>
-    <row r="390" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="390" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C390" s="16">
         <v>37.299999999999997</v>
       </c>
@@ -63809,7 +63813,7 @@
         <v>1.8837496674689476</v>
       </c>
     </row>
-    <row r="391" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="391" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C391" s="16">
         <v>37.4</v>
       </c>
@@ -63846,7 +63850,7 @@
         <v>1.8812818936378699</v>
       </c>
     </row>
-    <row r="392" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="392" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C392" s="16">
         <v>37.5</v>
       </c>
@@ -63883,7 +63887,7 @@
         <v>1.8788237930589022</v>
       </c>
     </row>
-    <row r="393" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="393" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C393" s="16">
         <v>37.6</v>
       </c>
@@ -63920,7 +63924,7 @@
         <v>1.8763753027009129</v>
       </c>
     </row>
-    <row r="394" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="394" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C394" s="16">
         <v>37.700000000000003</v>
       </c>
@@ -63957,7 +63961,7 @@
         <v>1.8739363601062728</v>
       </c>
     </row>
-    <row r="395" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="395" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C395" s="16">
         <v>37.799999999999997</v>
       </c>
@@ -63994,7 +63998,7 @@
         <v>1.8715069033841638</v>
       </c>
     </row>
-    <row r="396" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="396" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C396" s="16">
         <v>37.9</v>
       </c>
@@ -64031,7 +64035,7 @@
         <v>1.8690868712039816</v>
       </c>
     </row>
-    <row r="397" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="397" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C397" s="16">
         <v>38</v>
       </c>
@@ -64068,7 +64072,7 @@
         <v>1.8666762027888351</v>
       </c>
     </row>
-    <row r="398" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="398" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C398" s="16">
         <v>38.1</v>
       </c>
@@ -64105,7 +64109,7 @@
         <v>1.8642748379091323</v>
       </c>
     </row>
-    <row r="399" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="399" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C399" s="16">
         <v>38.200000000000003</v>
       </c>
@@ -64142,7 +64146,7 @@
         <v>1.8618827168762624</v>
       </c>
     </row>
-    <row r="400" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="400" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C400" s="16">
         <v>38.299999999999997</v>
       </c>
@@ -64179,7 +64183,7 @@
         <v>1.8594997805363636</v>
       </c>
     </row>
-    <row r="401" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="401" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C401" s="16">
         <v>38.4</v>
       </c>
@@ -64216,7 +64220,7 @@
         <v>1.8571259702641787</v>
       </c>
     </row>
-    <row r="402" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="402" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C402" s="16">
         <v>38.5</v>
       </c>
@@ -64253,7 +64257,7 @@
         <v>1.8547612279569987</v>
       </c>
     </row>
-    <row r="403" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="403" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C403" s="16">
         <v>38.6</v>
       </c>
@@ -64290,7 +64294,7 @@
         <v>1.8524054960286882</v>
       </c>
     </row>
-    <row r="404" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="404" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C404" s="16">
         <v>38.700000000000003</v>
       </c>
@@ -64327,7 +64331,7 @@
         <v>1.8500587174037959</v>
       </c>
     </row>
-    <row r="405" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="405" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C405" s="16">
         <v>38.799999999999997</v>
       </c>
@@ -64364,7 +64368,7 @@
         <v>1.8477208355117467</v>
       </c>
     </row>
-    <row r="406" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="406" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C406" s="16">
         <v>38.9</v>
       </c>
@@ -64401,7 +64405,7 @@
         <v>1.8453917942811138</v>
       </c>
     </row>
-    <row r="407" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="407" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C407" s="16">
         <v>39</v>
       </c>
@@ -64438,7 +64442,7 @@
         <v>1.8430715381339711</v>
       </c>
     </row>
-    <row r="408" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="408" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C408" s="16">
         <v>39.1</v>
       </c>
@@ -64475,7 +64479,7 @@
         <v>1.8407600119803214</v>
       </c>
     </row>
-    <row r="409" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="409" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C409" s="16">
         <v>39.200000000000003</v>
       </c>
@@ -64512,7 +64516,7 @@
         <v>1.8384571612126051</v>
       </c>
     </row>
-    <row r="410" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="410" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C410" s="16">
         <v>39.299999999999997</v>
       </c>
@@ -64549,7 +64553,7 @@
         <v>1.8361629317002788</v>
       </c>
     </row>
-    <row r="411" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="411" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C411" s="16">
         <v>39.4</v>
       </c>
@@ -64586,7 +64590,7 @@
         <v>1.8338772697844734</v>
       </c>
     </row>
-    <row r="412" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="412" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C412" s="16">
         <v>39.5</v>
       </c>
@@ -64623,7 +64627,7 @@
         <v>1.8316001222727216</v>
       </c>
     </row>
-    <row r="413" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="413" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C413" s="16">
         <v>39.6</v>
       </c>
@@ -64660,7 +64664,7 @@
         <v>1.8293314364337603</v>
       </c>
     </row>
-    <row r="414" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="414" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C414" s="16">
         <v>39.700000000000003</v>
       </c>
@@ -64697,7 +64701,7 @@
         <v>1.8270711599923997</v>
       </c>
     </row>
-    <row r="415" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="415" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C415" s="16">
         <v>39.799999999999997</v>
       </c>
@@ -64734,7 +64738,7 @@
         <v>1.8248192411244661</v>
       </c>
     </row>
-    <row r="416" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="416" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C416" s="16">
         <v>39.9</v>
       </c>
@@ -64771,7 +64775,7 @@
         <v>1.8225756284518098</v>
       </c>
     </row>
-    <row r="417" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="417" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C417" s="16">
         <v>40</v>
       </c>
@@ -64808,7 +64812,7 @@
         <v>1.8203402710373824</v>
       </c>
     </row>
-    <row r="418" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="418" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C418" s="16">
         <v>40.1</v>
       </c>
@@ -64845,7 +64849,7 @@
         <v>1.81811311838038</v>
       </c>
     </row>
-    <row r="419" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="419" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C419" s="16">
         <v>40.200000000000003</v>
       </c>
@@ -64882,7 +64886,7 @@
         <v>1.8158941204114503</v>
       </c>
     </row>
-    <row r="420" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="420" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C420" s="16">
         <v>40.299999999999997</v>
       </c>
@@ -64919,7 +64923,7 @@
         <v>1.813683227487966</v>
       </c>
     </row>
-    <row r="421" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="421" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C421" s="16">
         <v>40.4</v>
       </c>
@@ -64956,7 +64960,7 @@
         <v>1.8114803903893593</v>
       </c>
     </row>
-    <row r="422" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="422" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C422" s="16">
         <v>40.5</v>
       </c>
@@ -64993,7 +64997,7 @@
         <v>1.8092855603125197</v>
       </c>
     </row>
-    <row r="423" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="423" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C423" s="16">
         <v>40.6</v>
       </c>
@@ -65030,7 +65034,7 @@
         <v>1.8070986888672538</v>
       </c>
     </row>
-    <row r="424" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="424" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C424" s="16">
         <v>40.700000000000003</v>
       </c>
@@ -65067,7 +65071,7 @@
         <v>1.8049197280718026</v>
       </c>
     </row>
-    <row r="425" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="425" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C425" s="16">
         <v>40.799999999999997</v>
       </c>
@@ -65104,7 +65108,7 @@
         <v>1.802748630348421</v>
       </c>
     </row>
-    <row r="426" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="426" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C426" s="16">
         <v>40.9</v>
       </c>
@@ -65141,7 +65145,7 @@
         <v>1.8005853485190146</v>
       </c>
     </row>
-    <row r="427" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="427" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C427" s="16">
         <v>41</v>
       </c>
@@ -65178,7 +65182,7 @@
         <v>1.7984298358008328</v>
       </c>
     </row>
-    <row r="428" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="428" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C428" s="16">
         <v>41.1</v>
       </c>
@@ -65215,7 +65219,7 @@
         <v>1.7962820458022204</v>
       </c>
     </row>
-    <row r="429" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="429" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C429" s="16">
         <v>41.2</v>
       </c>
@@ -65252,7 +65256,7 @@
         <v>1.7941419325184238</v>
       </c>
     </row>
-    <row r="430" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="430" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C430" s="16">
         <v>41.3</v>
       </c>
@@ -65289,7 +65293,7 @@
         <v>1.7920094503274524</v>
       </c>
     </row>
-    <row r="431" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="431" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C431" s="16">
         <v>41.4</v>
       </c>
@@ -65326,7 +65330,7 @@
         <v>1.7898845539859931</v>
       </c>
     </row>
-    <row r="432" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="432" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C432" s="16">
         <v>41.5</v>
       </c>
@@ -65363,7 +65367,7 @@
         <v>1.7877671986253794</v>
       </c>
     </row>
-    <row r="433" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="433" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C433" s="16">
         <v>41.6</v>
       </c>
@@ -65400,7 +65404,7 @@
         <v>1.7856573397476112</v>
       </c>
     </row>
-    <row r="434" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="434" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C434" s="16">
         <v>41.7</v>
       </c>
@@ -65437,7 +65441,7 @@
         <v>1.7835549332214289</v>
       </c>
     </row>
-    <row r="435" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="435" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C435" s="16">
         <v>41.8</v>
       </c>
@@ -65474,7 +65478,7 @@
         <v>1.7814599352784342</v>
       </c>
     </row>
-    <row r="436" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="436" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C436" s="16">
         <v>41.9</v>
       </c>
@@ -65511,7 +65515,7 @@
         <v>1.779372302509264</v>
       </c>
     </row>
-    <row r="437" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="437" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C437" s="16">
         <v>42</v>
       </c>
@@ -65548,7 +65552,7 @@
         <v>1.7772919918598131</v>
       </c>
     </row>
-    <row r="438" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="438" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C438" s="16">
         <v>42.1</v>
       </c>
@@ -65585,7 +65589,7 @@
         <v>1.7752189606275042</v>
       </c>
     </row>
-    <row r="439" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="439" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C439" s="16">
         <v>42.2</v>
       </c>
@@ -65622,7 +65626,7 @@
         <v>1.7731531664576059</v>
       </c>
     </row>
-    <row r="440" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="440" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C440" s="16">
         <v>42.3</v>
       </c>
@@ -65659,7 +65663,7 @@
         <v>1.771094567339599</v>
       </c>
     </row>
-    <row r="441" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="441" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C441" s="16">
         <v>42.4</v>
       </c>
@@ -65696,7 +65700,7 @@
         <v>1.7690431216035887</v>
       </c>
     </row>
-    <row r="442" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="442" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C442" s="16">
         <v>42.5</v>
       </c>
@@ -65733,7 +65737,7 @@
         <v>1.766998787916759</v>
       </c>
     </row>
-    <row r="443" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="443" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C443" s="16">
         <v>42.6</v>
       </c>
@@ -65770,7 +65774,7 @@
         <v>1.7649615252798792</v>
       </c>
     </row>
-    <row r="444" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="444" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C444" s="16">
         <v>42.7</v>
       </c>
@@ -65807,7 +65811,7 @@
         <v>1.762931293023847</v>
       </c>
     </row>
-    <row r="445" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="445" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C445" s="16">
         <v>42.8</v>
       </c>
@@ -65844,7 +65848,7 @@
         <v>1.7609080508062802</v>
       </c>
     </row>
-    <row r="446" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="446" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C446" s="16">
         <v>42.9</v>
       </c>
@@ -65881,7 +65885,7 @@
         <v>1.7588917586081494</v>
       </c>
     </row>
-    <row r="447" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="447" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C447" s="16">
         <v>43</v>
       </c>
@@ -65918,7 +65922,7 @@
         <v>1.7568823767304533</v>
       </c>
     </row>
-    <row r="448" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="448" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C448" s="16">
         <v>43.1</v>
       </c>
@@ -65955,7 +65959,7 @@
         <v>1.7548798657909364</v>
       </c>
     </row>
-    <row r="449" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="449" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C449" s="16">
         <v>43.2</v>
       </c>
@@ -65992,7 +65996,7 @@
         <v>1.7528841867208453</v>
       </c>
     </row>
-    <row r="450" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="450" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C450" s="16">
         <v>43.3</v>
       </c>
@@ -66029,7 +66033,7 @@
         <v>1.7508953007617298</v>
       </c>
     </row>
-    <row r="451" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="451" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C451" s="16">
         <v>43.4</v>
       </c>
@@ -66066,7 +66070,7 @@
         <v>1.7489131694622801</v>
       </c>
     </row>
-    <row r="452" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="452" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C452" s="16">
         <v>43.5</v>
       </c>
@@ -66103,7 +66107,7 @@
         <v>1.7469377546752038</v>
       </c>
     </row>
-    <row r="453" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="453" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C453" s="16">
         <v>43.6</v>
       </c>
@@ -66140,7 +66144,7 @@
         <v>1.7449690185541435</v>
       </c>
     </row>
-    <row r="454" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="454" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C454" s="16">
         <v>43.7</v>
       </c>
@@ -66177,7 +66181,7 @@
         <v>1.7430069235506309</v>
       </c>
     </row>
-    <row r="455" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="455" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C455" s="16">
         <v>43.8</v>
       </c>
@@ -66214,7 +66218,7 @@
         <v>1.7410514324110793</v>
       </c>
     </row>
-    <row r="456" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="456" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C456" s="16">
         <v>43.9</v>
       </c>
@@ -66251,7 +66255,7 @@
         <v>1.7391025081738118</v>
       </c>
     </row>
-    <row r="457" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="457" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C457" s="16">
         <v>44</v>
       </c>
@@ -66288,7 +66292,7 @@
         <v>1.7371601141661286</v>
       </c>
     </row>
-    <row r="458" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="458" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C458" s="16">
         <v>44.1</v>
       </c>
@@ -66325,7 +66329,7 @@
         <v>1.7352242140014071</v>
       </c>
     </row>
-    <row r="459" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="459" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C459" s="16">
         <v>44.2</v>
       </c>
@@ -66362,7 +66366,7 @@
         <v>1.7332947715762403</v>
       </c>
     </row>
-    <row r="460" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="460" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C460" s="16">
         <v>44.3</v>
       </c>
@@ -66399,7 +66403,7 @@
         <v>1.7313717510676081</v>
       </c>
     </row>
-    <row r="461" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="461" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C461" s="16">
         <v>44.4</v>
       </c>
@@ -66436,7 +66440,7 @@
         <v>1.7294551169300836</v>
       </c>
     </row>
-    <row r="462" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="462" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C462" s="16">
         <v>44.5</v>
       </c>
@@ -66473,7 +66477,7 @@
         <v>1.7275448338930741</v>
       </c>
     </row>
-    <row r="463" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="463" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C463" s="16">
         <v>44.6</v>
       </c>
@@ -66510,7 +66514,7 @@
         <v>1.7256408669580952</v>
       </c>
     </row>
-    <row r="464" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="464" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C464" s="16">
         <v>44.7</v>
       </c>
@@ -66547,7 +66551,7 @@
         <v>1.7237431813960769</v>
       </c>
     </row>
-    <row r="465" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="465" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C465" s="16">
         <v>44.8</v>
       </c>
@@ -66584,7 +66588,7 @@
         <v>1.7218517427447029</v>
       </c>
     </row>
-    <row r="466" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="466" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C466" s="16">
         <v>44.9</v>
       </c>
@@ -66621,7 +66625,7 @@
         <v>1.7199665168057834</v>
       </c>
     </row>
-    <row r="467" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="467" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C467" s="16">
         <v>45</v>
       </c>
@@ -66658,7 +66662,7 @@
         <v>1.7180874696426565</v>
       </c>
     </row>
-    <row r="468" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="468" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C468" s="16">
         <v>45.1</v>
       </c>
@@ -66695,7 +66699,7 @@
         <v>1.716214567577623</v>
       </c>
     </row>
-    <row r="469" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="469" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C469" s="16">
         <v>45.2</v>
       </c>
@@ -66732,7 +66736,7 @@
         <v>1.7143477771894118</v>
       </c>
     </row>
-    <row r="470" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="470" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C470" s="16">
         <v>45.3</v>
       </c>
@@ -66769,7 +66773,7 @@
         <v>1.7124870653106736</v>
       </c>
     </row>
-    <row r="471" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="471" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C471" s="16">
         <v>45.4</v>
       </c>
@@ -66806,7 +66810,7 @@
         <v>1.7106323990255077</v>
       </c>
     </row>
-    <row r="472" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="472" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C472" s="16">
         <v>45.5</v>
       </c>
@@ -66843,7 +66847,7 @@
         <v>1.7087837456670145</v>
       </c>
     </row>
-    <row r="473" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="473" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C473" s="16">
         <v>45.6</v>
       </c>
@@ -66880,7 +66884,7 @@
         <v>1.7069410728148802</v>
       </c>
     </row>
-    <row r="474" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="474" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C474" s="16">
         <v>45.7</v>
       </c>
@@ -66917,7 +66921,7 @@
         <v>1.7051043482929886</v>
       </c>
     </row>
-    <row r="475" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="475" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C475" s="16">
         <v>45.8</v>
       </c>
@@ -66954,7 +66958,7 @@
         <v>1.7032735401670605</v>
       </c>
     </row>
-    <row r="476" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="476" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C476" s="16">
         <v>45.9</v>
       </c>
@@ -66991,7 +66995,7 @@
         <v>1.7014486167423231</v>
       </c>
     </row>
-    <row r="477" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="477" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C477" s="16">
         <v>46</v>
       </c>
@@ -67028,7 +67032,7 @@
         <v>1.6996295465612039</v>
       </c>
     </row>
-    <row r="478" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="478" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C478" s="16">
         <v>46.1</v>
       </c>
@@ -67065,7 +67069,7 @@
         <v>1.6978162984010539</v>
       </c>
     </row>
-    <row r="479" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="479" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C479" s="16">
         <v>46.2</v>
       </c>
@@ -67102,7 +67106,7 @@
         <v>1.6960088412718977</v>
       </c>
     </row>
-    <row r="480" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="480" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C480" s="16">
         <v>46.3</v>
       </c>
@@ -67139,7 +67143,7 @@
         <v>1.6942071444142066</v>
       </c>
     </row>
-    <row r="481" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="481" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C481" s="16">
         <v>46.4</v>
       </c>
@@ -67176,7 +67180,7 @@
         <v>1.6924111772967023</v>
       </c>
     </row>
-    <row r="482" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="482" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C482" s="16">
         <v>46.5</v>
       </c>
@@ -67213,7 +67217,7 @@
         <v>1.6906209096141831</v>
       </c>
     </row>
-    <row r="483" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="483" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C483" s="16">
         <v>46.6</v>
       </c>
@@ -67250,7 +67254,7 @@
         <v>1.688836311285375</v>
       </c>
     </row>
-    <row r="484" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="484" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C484" s="16">
         <v>46.7</v>
       </c>
@@ -67287,7 +67291,7 @@
         <v>1.6870573524508112</v>
       </c>
     </row>
-    <row r="485" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="485" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C485" s="16">
         <v>46.8</v>
       </c>
@@ -67324,7 +67328,7 @@
         <v>1.685284003470731</v>
       </c>
     </row>
-    <row r="486" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="486" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C486" s="16">
         <v>46.9</v>
       </c>
@@ -67361,7 +67365,7 @@
         <v>1.6835162349230077</v>
       </c>
     </row>
-    <row r="487" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="487" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C487" s="16">
         <v>47</v>
       </c>
@@ -67398,7 +67402,7 @@
         <v>1.6817540176010972</v>
       </c>
     </row>
-    <row r="488" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="488" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C488" s="16">
         <v>47.1</v>
       </c>
@@ -67435,7 +67439,7 @@
         <v>1.6799973225120122</v>
       </c>
     </row>
-    <row r="489" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="489" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C489" s="16">
         <v>47.2</v>
       </c>
@@ -67472,7 +67476,7 @@
         <v>1.6782461208743178</v>
       </c>
     </row>
-    <row r="490" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="490" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C490" s="16">
         <v>47.3</v>
       </c>
@@ -67509,7 +67513,7 @@
         <v>1.676500384116151</v>
       </c>
     </row>
-    <row r="491" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="491" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C491" s="16">
         <v>47.4</v>
       </c>
@@ -67546,7 +67550,7 @@
         <v>1.6747600838732641</v>
       </c>
     </row>
-    <row r="492" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="492" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C492" s="16">
         <v>47.5</v>
       </c>
@@ -67583,7 +67587,7 @@
         <v>1.6730251919870875</v>
       </c>
     </row>
-    <row r="493" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="493" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C493" s="16">
         <v>47.6</v>
       </c>
@@ -67620,7 +67624,7 @@
         <v>1.6712956805028165</v>
       </c>
     </row>
-    <row r="494" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="494" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C494" s="16">
         <v>47.7</v>
       </c>
@@ -67657,7 +67661,7 @@
         <v>1.6695715216675204</v>
       </c>
     </row>
-    <row r="495" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="495" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C495" s="16">
         <v>47.8</v>
       </c>
@@ -67694,7 +67698,7 @@
         <v>1.6678526879282711</v>
       </c>
     </row>
-    <row r="496" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="496" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C496" s="16">
         <v>47.9</v>
       </c>
@@ -67731,7 +67735,7 @@
         <v>1.6661391519302928</v>
       </c>
     </row>
-    <row r="497" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="497" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C497" s="16">
         <v>48</v>
       </c>
@@ -67768,7 +67772,7 @@
         <v>1.664430886515136</v>
       </c>
     </row>
-    <row r="498" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="498" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C498" s="16">
         <v>48.1</v>
       </c>
@@ -67805,7 +67809,7 @@
         <v>1.6627278647188675</v>
       </c>
     </row>
-    <row r="499" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="499" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C499" s="16">
         <v>48.2</v>
       </c>
@@ -67842,7 +67846,7 @@
         <v>1.6610300597702843</v>
       </c>
     </row>
-    <row r="500" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="500" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C500" s="16">
         <v>48.3</v>
       </c>
@@ -67879,7 +67883,7 @@
         <v>1.659337445089144</v>
       </c>
     </row>
-    <row r="501" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="501" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C501" s="16">
         <v>48.4</v>
       </c>
@@ -67916,7 +67920,7 @@
         <v>1.6576499942844198</v>
       </c>
     </row>
-    <row r="502" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="502" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C502" s="16">
         <v>48.5</v>
       </c>
@@ -67953,7 +67957,7 @@
         <v>1.6559676811525699</v>
       </c>
     </row>
-    <row r="503" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="503" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C503" s="16">
         <v>48.6</v>
       </c>
@@ -67990,7 +67994,7 @@
         <v>1.6542904796758295</v>
       </c>
     </row>
-    <row r="504" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="504" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C504" s="16">
         <v>48.7</v>
       </c>
@@ -68027,7 +68031,7 @@
         <v>1.6526183640205216</v>
       </c>
     </row>
-    <row r="505" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="505" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C505" s="16">
         <v>48.8</v>
       </c>
@@ -68064,7 +68068,7 @@
         <v>1.6509513085353826</v>
       </c>
     </row>
-    <row r="506" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="506" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C506" s="16">
         <v>48.9</v>
       </c>
@@ -68101,7 +68105,7 @@
         <v>1.6492892877499143</v>
       </c>
     </row>
-    <row r="507" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="507" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C507" s="16">
         <v>49</v>
       </c>
@@ -68138,7 +68142,7 @@
         <v>1.6476322763727453</v>
       </c>
     </row>
-    <row r="508" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="508" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C508" s="16">
         <v>49.1</v>
       </c>
@@ -68175,7 +68179,7 @@
         <v>1.6459802492900162</v>
       </c>
     </row>
-    <row r="509" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="509" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C509" s="16">
         <v>49.2</v>
       </c>
@@ -68212,7 +68216,7 @@
         <v>1.6443331815637818</v>
       </c>
     </row>
-    <row r="510" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="510" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C510" s="16">
         <v>49.3</v>
       </c>
@@ -68249,7 +68253,7 @@
         <v>1.6426910484304278</v>
       </c>
     </row>
-    <row r="511" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="511" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C511" s="16">
         <v>49.4</v>
       </c>
@@ -68286,7 +68290,7 @@
         <v>1.6410538252991094</v>
       </c>
     </row>
-    <row r="512" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="512" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C512" s="16">
         <v>49.5</v>
       </c>
@@ -68323,7 +68327,7 @@
         <v>1.6394214877502025</v>
       </c>
     </row>
-    <row r="513" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="513" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C513" s="16">
         <v>49.6</v>
       </c>
@@ -68360,7 +68364,7 @@
         <v>1.6377940115337759</v>
       </c>
     </row>
-    <row r="514" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="514" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C514" s="16">
         <v>49.7</v>
       </c>
@@ -68397,7 +68401,7 @@
         <v>1.6361713725680764</v>
       </c>
     </row>
-    <row r="515" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="515" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C515" s="16">
         <v>49.8</v>
       </c>
@@ -68434,7 +68438,7 @@
         <v>1.6345535469380339</v>
       </c>
     </row>
-    <row r="516" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="516" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C516" s="16">
         <v>49.9</v>
       </c>
@@ -68471,7 +68475,7 @@
         <v>1.6329405108937791</v>
       </c>
     </row>
-    <row r="517" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="517" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C517" s="16">
         <v>50</v>
       </c>
@@ -68508,7 +68512,7 @@
         <v>1.6313322408491815</v>
       </c>
     </row>
-    <row r="518" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="518" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C518" s="16"/>
       <c r="D518" s="36"/>
       <c r="E518" s="35"/>
@@ -68519,7 +68523,7 @@
       <c r="J518" s="36"/>
       <c r="K518" s="35"/>
     </row>
-    <row r="519" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="519" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C519" s="16"/>
       <c r="D519" s="36"/>
       <c r="E519" s="35"/>
@@ -68546,14 +68550,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7D39D8D-3231-4118-8E3B-E252A5BB154D}">
   <dimension ref="A1:M24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="15" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -68561,7 +68565,7 @@
         <v>1737.4</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>101</v>
       </c>
@@ -68569,7 +68573,7 @@
         <v>4902.8</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -68577,26 +68581,26 @@
         <v>398600</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="79" t="s">
+    <row r="4" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="80"/>
-      <c r="F5" s="79" t="s">
+      <c r="D5" s="78"/>
+      <c r="F5" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="80"/>
-      <c r="I5" s="79" t="s">
+      <c r="G5" s="78"/>
+      <c r="I5" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="80"/>
-      <c r="L5" s="79" t="s">
+      <c r="J5" s="78"/>
+      <c r="L5" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="80"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M5" s="78"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
@@ -68620,7 +68624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
@@ -68643,7 +68647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -68666,12 +68670,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="77">
+    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="79">
         <f>SQRT(D8*((2/D7)-(1/D6)))</f>
         <v>1.9186316480773129</v>
       </c>
-      <c r="D9" s="78"/>
+      <c r="D9" s="80"/>
       <c r="F9" s="6" t="s">
         <v>0</v>
       </c>
@@ -68688,12 +68692,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F10" s="77">
+    <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F10" s="79">
         <f>($G$6-$G$7*EXP((G8)/($G$9*9.81)))/(EXP((G8)/($G$9*9.81)))</f>
         <v>69988.034237650369</v>
       </c>
-      <c r="G10" s="78"/>
+      <c r="G10" s="80"/>
       <c r="I10" s="1" t="s">
         <v>19</v>
       </c>
@@ -68701,7 +68705,7 @@
         <v>0.86899999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I11" s="1" t="s">
         <v>17</v>
       </c>
@@ -68710,11 +68714,11 @@
         <v>4.9939999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C12" s="79" t="s">
+    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="80"/>
+      <c r="D12" s="78"/>
       <c r="I12" s="6" t="s">
         <v>18</v>
       </c>
@@ -68723,24 +68727,24 @@
         <v>0.64900000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="5">
         <v>3558</v>
       </c>
-      <c r="F13" s="79" t="s">
+      <c r="F13" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="80"/>
-      <c r="I13" s="79">
+      <c r="G13" s="78"/>
+      <c r="I13" s="77">
         <f>J12+J11</f>
         <v>5.6429999999999998</v>
       </c>
-      <c r="J13" s="80"/>
-    </row>
-    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J13" s="78"/>
+    </row>
+    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C14" s="6" t="s">
         <v>15</v>
       </c>
@@ -68754,12 +68758,12 @@
         <v>36543</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C15" s="79">
+    <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="77">
         <f>(D13+D14)/2</f>
         <v>3558</v>
       </c>
-      <c r="D15" s="80"/>
+      <c r="D15" s="78"/>
       <c r="F15" s="1" t="s">
         <v>6</v>
       </c>
@@ -68767,19 +68771,19 @@
         <v>1849.8</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G16" s="2">
         <v>1280</v>
       </c>
-      <c r="I16" s="79" t="s">
+      <c r="I16" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="J16" s="80"/>
-    </row>
-    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J16" s="78"/>
+    </row>
+    <row r="17" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F17" s="6" t="s">
         <v>0</v>
       </c>
@@ -68793,16 +68797,16 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="18" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C18" s="79" t="s">
+    <row r="18" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="77" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="80"/>
-      <c r="F18" s="77">
+      <c r="D18" s="78"/>
+      <c r="F18" s="79">
         <f>EXP(G16/(G17*9.81))*(G14+G15) - (G14+G15)</f>
         <v>17465.040076315519</v>
       </c>
-      <c r="G18" s="78"/>
+      <c r="G18" s="80"/>
       <c r="I18" s="1" t="s">
         <v>97</v>
       </c>
@@ -68810,7 +68814,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" s="4" t="s">
         <v>1</v>
       </c>
@@ -68825,7 +68829,7 @@
         <v>82656</v>
       </c>
     </row>
-    <row r="20" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C20" s="6" t="s">
         <v>4</v>
       </c>
@@ -68840,30 +68844,37 @@
         <v>17465</v>
       </c>
     </row>
-    <row r="21" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="77">
+    <row r="21" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="79">
         <f>2*PI()*SQRT(D19^3/D20)/60/60/24</f>
         <v>2.44459204577962E-2</v>
       </c>
-      <c r="D21" s="78"/>
-      <c r="I21" s="77">
+      <c r="D21" s="80"/>
+      <c r="I21" s="79">
         <f>(J17-J18)/((J19)/(J20))+J18</f>
         <v>1849.3733062330625</v>
       </c>
-      <c r="J21" s="78"/>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="J21" s="80"/>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
         <v>104</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C18:D18"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="C5:D5"/>
@@ -68872,13 +68883,6 @@
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
